--- a/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
@@ -1959,7 +1959,7 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けですね。続きは、またいつか。</t>
+          <t xml:space="preserve">決まらなかったですね。続きは、またいつか。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
@@ -372,7 +372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -430,22 +430,22 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.standard.hit[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.standard.hit[1]</t>
+          <t xml:space="preserve">atk.standard.normal[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -455,29 +455,29 @@
       </c>
       <c r="F2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立てる。あなたたち相手に、ここで終われない。</t>
+          <t xml:space="preserve">いくよ！</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.standard.hit[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.standard.hit[2]</t>
+          <t xml:space="preserve">atk.standard.normal[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -487,29 +487,29 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来た意味を、自分で潰すわけにはいかない。</t>
+          <t xml:space="preserve">まだまだ！</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.standard.win[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.standard.win[1]</t>
+          <t xml:space="preserve">atk.standard.normal[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -519,29 +519,29 @@
       </c>
       <c r="F4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">解雇されてから、ここまで来た。あそこに、証明できたと思う。</t>
+          <t xml:space="preserve">負けないから！</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.normal.standard.win[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.normal[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.standard.win[2]</t>
+          <t xml:space="preserve">atk.standard.normal[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -551,1004 +551,2572 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの団体で出来なかったことを、ここで完成させる。だから勝つ。</t>
+          <t xml:space="preserve">ここからよ！</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.lose[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.normal[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.lose[1]</t>
+          <t xml:space="preserve">bigmove.standard.normal[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……負けました。すみません。</t>
+          <t xml:space="preserve">いくよ…これで決める！</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.lose[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.normal[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.lose[2]</t>
+          <t xml:space="preserve">bigmove.standard.normal[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです。……本当に、悔しい。</t>
+          <t xml:space="preserve">ここで…終わりだ！</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.lose[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.normal[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.lose[3]</t>
+          <t xml:space="preserve">bigmove.standard.normal[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てませんでした。……申し訳ないです。</t>
+          <t xml:space="preserve">全部出し切る…！</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.petition[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.normal[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.petition[1]</t>
+          <t xml:space="preserve">climax.standard.normal[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お願いがあります。あの人とやらせてください。</t>
+          <t xml:space="preserve">（…ここからだ）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.petition[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.normal[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.petition[2]</t>
+          <t xml:space="preserve">climax.standard.normal[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても、あの人とやりたいんです。……お願いします。</t>
+          <t xml:space="preserve">（負けない…！）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.petition[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.petition[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わがままだとは分かってます。それでも、組んでほしいんです。</t>
+          <t xml:space="preserve">くっ…まだ…まだだ…！</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.sendoff[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.sendoff[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます! ……行ってきます。</t>
+          <t xml:space="preserve">効いた…けど…負けない…！</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.sendoff[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.sendoff[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。必ず、勝ってきます。</t>
+          <t xml:space="preserve">はぁ…はぁ…立てる…まだ…</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.sendoff[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.normal.hit[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.sendoff[3]</t>
+          <t xml:space="preserve">standard.normal.hit[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ありがとうございます。やってきます。</t>
+          <t xml:space="preserve">まだ立てる。あなたたち相手に、ここで終われない。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.normal.hit[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.win[1]</t>
+          <t xml:space="preserve">standard.normal.hit[2]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……ありがとうございました。</t>
+          <t xml:space="preserve">……来た意味を、自分で潰すわけにはいかない。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.normal.win[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.win[2]</t>
+          <t xml:space="preserve">standard.normal.win[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました! ……見ててくれましたか。</t>
+          <t xml:space="preserve">解雇されてから、ここまで来た。あそこに、証明できたと思う。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.win[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.normal.win[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.win[3]</t>
+          <t xml:space="preserve">standard.normal.win[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てました。……無駄にしなくて、よかった。</t>
+          <t xml:space="preserve">あの団体で出来なかったことを、ここで完成させる。だから勝つ。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal._accept[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal._accept[1]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けて立ちます。正面から来てください。</t>
+          <t xml:space="preserve">……動けない</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal._accept[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal._accept[2]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名指しされて、引くわけにはいきません。</t>
+          <t xml:space="preserve">……間に合わない</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal._accept[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal._accept[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わかりました。全力でいきます。</t>
+          <t xml:space="preserve">させない！</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.draw[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.draw[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかず、か。すっきりしませんね。</t>
+          <t xml:space="preserve">まだだ！</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.draw[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.draw[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決まらなかったですね。続きは、またいつか。</t>
+          <t xml:space="preserve">渡さないよ！</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.draw[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.draw[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ててないし、負けてもいない。それだけです。</t>
+          <t xml:space="preserve">合わせて！</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.lose[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.lose[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。あなたのほうが上だった。</t>
+          <t xml:space="preserve">いくよ、二人で！</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.lose[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.lose[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい。……でも、受けたことに後悔はないです。</t>
+          <t xml:space="preserve">息を合わせよう！</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.lose[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.lose[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">完敗。……この借りは返します。</t>
+          <t xml:space="preserve">任せて！</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.win[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.win[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けて正解でした。いい試合だった。</t>
+          <t xml:space="preserve">交代だよ！</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.win[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.win[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はわたしが上でしたね。強かったですよ。</t>
+          <t xml:space="preserve">ここからは私が行く！</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.win[3]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_normal.win[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。いい相手でしたよ、あなた。</t>
+          <t xml:space="preserve">{partner}…ごめん。私が決めきれてたら…</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.normal.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.standard[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちら側とは、方針が違う。私たちは私たちの道を行く。</t>
+          <t xml:space="preserve">{partner}、悔しいね。次は絶対、勝とう。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.normal.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.standard[1]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……実感が湧かない。あの人がいない団体なんて。</t>
+          <t xml:space="preserve">{partner}、ありがとう。二人だから勝てたよ。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.normal.standard[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.standard[2]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これから、どうなるんだろう。</t>
+          <t xml:space="preserve">やった…{partner}となら勝てるって、信じてた！</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.normal.standard[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.lose[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.standard[1]</t>
+          <t xml:space="preserve">standard_normal.lose[1]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪いけど、あたし、あっちに行くことにした。</t>
+          <t xml:space="preserve">……負けました。すみません。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.normal.standard[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.lose[2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.standard[2]</t>
+          <t xml:space="preserve">standard_normal.lose[2]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">色々、考えた結果です。どうかご理解を。</t>
+          <t xml:space="preserve">悔しいです。……本当に、悔しい。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.normal.standard[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.lose[3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal.standard[1]</t>
+          <t xml:space="preserve">standard_normal.lose[3]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、うちの派閥には、それなりの配慮が必要だと思いますが。</t>
+          <t xml:space="preserve">勝てませんでした。……申し訳ないです。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.normal.standard[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.petition[1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.petition[1]</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、お願いがあります。あの人とやらせてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.petition[2]</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.petition[2]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">どうしても、あの人とやりたいんです。……お願いします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.petition[3]</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.petition[3]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わがままだとは分かってます。それでも、組んでほしいんです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.sendoff[1]</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.sendoff[1]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます! ……行ってきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.sendoff[2]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.sendoff[2]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます。必ず、勝ってきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.sendoff[3]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.sendoff[3]</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ありがとうございます。やってきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.win[1]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.win[1]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。……ありがとうございました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.win[2]</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.win[2]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりました! ……見ててくれましたか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_normal.win[3]</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.win[3]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝てました。……無駄にしなくて、よかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal._accept[1]</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal._accept[1]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受けて立ちます。正面から来てください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal._accept[2]</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal._accept[2]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">名指しされて、引くわけにはいきません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal._accept[3]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal._accept[3]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わかりました。全力でいきます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.draw[1]</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.draw[1]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決着つかず、か。すっきりしませんね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.draw[2]</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.draw[2]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決まらなかったですね。続きは、またいつか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.draw[3]</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.draw[3]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ててないし、負けてもいない。それだけです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.lose[1]</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.lose[1]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けました。あなたのほうが上だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.lose[2]</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.lose[2]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔しい。……でも、受けたことに後悔はないです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.lose[3]</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.lose[3]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">完敗。……この借りは返します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.win[1]</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.win[1]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受けて正解でした。いい試合だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.win[2]</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.win[2]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日はわたしが上でしたね。強かったですよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_normal.win[3]</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_normal.win[3]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。いい相手でしたよ、あなた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">src/data-faction-dialogue.js</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">normal.standard[2]</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr" s="2">
+      <c r="C57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">話しておきたいことがあります。時間を取ってほしい。</t>
+      <c r="F57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今のままじゃ、立ち行かない。誰かが、声を上げないと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">上の人には、もう期待できない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……気づけば、睨み合う理由がどこかに消えてたね。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ、お互い、大人になったってことかな。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">話はもう済んだ。後は、リングで示すだけ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">引き下がる理由は、もう、どこにもない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.normal.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……今日は、負け。だけど、組は終わらない</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.normal.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、こうはいかせない</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.normal.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……（呼吸だけが響く）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.normal.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……くっ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今夜の決着は、これで充分だろう</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.normal.high[2]</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.high[2]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あんたの組とは、もう距離を置かせてもらう</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.normal.low[1]</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.low[1]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝てた</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.normal.mid[1]</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.mid[1]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った。それで充分</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日のリングは、あんたとあたしのためにある</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.normal.high[2]</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.high[2]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">言葉ではもう、何も伝わらない。だからリングで</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.normal.low[1]</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.low[1]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">リングで、会いましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.normal.mid[1]</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.mid[1]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日で、片付ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受けます。リングで会いましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.normal.high[2]</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.high[2]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">退きません。今日は、決着のときだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.normal.low[1]</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.low[1]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">リングで</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.normal.mid[1]</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.mid[1]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">分かった。受ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.normal.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けた。あとは任せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.normal.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……託す</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.normal.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やられた。次は支える側に回る</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った。これからはわたしが先頭に立つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日、あなたの座を奪いに来た</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.normal.high[2]</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.high[2]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ずっとこの日を待っていた</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal.high[1]</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受けて立つ。リングで会おう</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H36"/>
+  <autoFilter ref="A1:H85"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
@@ -279,12 +279,12 @@
     <row r="6">
       <c r="A6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">小森さなえ</t>
+          <t xml:space="preserve">浜竹美咲</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Brawler</t>
+          <t xml:space="preserve">Grappler</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
@@ -294,36 +294,36 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">ムードメーカー</t>
+          <t xml:space="preserve">引き出し上手、忠誠心</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">浜竹美咲</t>
+          <t xml:space="preserve">椿山みさき</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grappler</t>
+          <t xml:space="preserve">Allround</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Neutral</t>
+          <t xml:space="preserve">Babyface</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">引き出し上手、忠誠心</t>
+          <t xml:space="preserve">引き出し上手、華、負けず嫌い</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">椿山みさき</t>
+          <t xml:space="preserve">南谷杏</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -333,12 +333,12 @@
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Babyface</t>
+          <t xml:space="preserve">Neutral</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">引き出し上手、華、負けず嫌い</t>
+          <t xml:space="preserve">ファンサービス</t>
         </is>
       </c>
     </row>
@@ -372,7 +372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H538"/>
+  <dimension ref="A1:H540"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="F77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……来なよ。相手してあげる</t>
+          <t xml:space="preserve">……来て。ちゃんと相手するよ</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">噓でしょ？……こんなはずじゃ……</t>
+          <t xml:space="preserve">嘘でしょ？……こんなはずじゃ……</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見たか！ 私が格下だなんて、もう言わせない……！</t>
+          <t xml:space="preserve">見て！ 私が格下だなんて、もう言わせない……！</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます! ……行ってきます。</t>
+          <t xml:space="preserve">ありがとうございます！ ……行ってきます。</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました! ……見ててくれましたか。</t>
+          <t xml:space="preserve">やりました！ ……見ててくれましたか。</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はわたしが上でしたね。強かったですよ。</t>
+          <t xml:space="preserve">今日は私が上でしたね。強かったですよ。</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトがある限り、わたしは終わらない</t>
+          <t xml:space="preserve">このベルトがある限り、私は終わらない</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしを追い出す気？ そう簡単にはいかないわよ</t>
+          <t xml:space="preserve">私を追い出す気？ そう簡単にはいかないわよ</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ終わらない。わたしはまだ闘える</t>
+          <t xml:space="preserve">まだ終わらない。私はまだ闘える</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体がある限り、わたしはリングに立つ</t>
+          <t xml:space="preserve">体がある限り、私はリングに立つ</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしがいなくなって寂しくなるね</t>
+          <t xml:space="preserve">私がいなくなって寂しくなるね</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが、あたしの全部だった</t>
+          <t xml:space="preserve">ここが、私の全部だった</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしの物語、こんなところで終わりなの…？</t>
+          <t xml:space="preserve">私の物語、こんなところで終わりなの…？</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のリングは、あんたとあたしのためにある</t>
+          <t xml:space="preserve">今日のリングは、あなたと私のためにある</t>
         </is>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った。これからはわたしが先頭に立つ</t>
+          <t xml:space="preserve">勝った。これからは私が先頭に立つ</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.normal[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.normal[1]</t>
+          <t xml:space="preserve">autumnWarChampion.standard.normal[1]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr" s="2">
@@ -8748,14 +8748,14 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合の最後の5分間は特別でした。全力を出せた気がします</t>
+          <t xml:space="preserve">団体の代表として戦い抜けたことを、誇りに思います。</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.normal[1]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.normal[2]</t>
+          <t xml:space="preserve">bestMatch.standard.normal[1]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr" s="2">
@@ -8780,14 +8780,14 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わった瞬間、全部出し切ったのがわかる。そんな試合でした</t>
+          <t xml:space="preserve">あの試合の最後の5分間は特別でした。全力を出せた気がします</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.normal[2]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[1]</t>
+          <t xml:space="preserve">bestMatch.standard.normal[2]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr" s="2">
@@ -8812,14 +8812,14 @@
       </c>
       <c r="F263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトの重さを、毎日感じています。だから強くなれると思ってる</t>
+          <t xml:space="preserve">終わった瞬間、全部出し切ったのがわかる。そんな試合でした</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.normal[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[2]</t>
+          <t xml:space="preserve">champion.standard.normal[1]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr" s="2">
@@ -8844,14 +8844,14 @@
       </c>
       <c r="F264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンであることは誇りです。逃げずに守り抜くよ</t>
+          <t xml:space="preserve">このベルトの重さを、毎日感じています。だから強くなれると思ってる</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.normal[2]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.normal[1]</t>
+          <t xml:space="preserve">champion.standard.normal[2]</t>
         </is>
       </c>
       <c r="E265" t="inlineStr" s="2">
@@ -8876,14 +8876,14 @@
       </c>
       <c r="F265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後悔はない。一試合も。…本当に良い現役生活でした</t>
+          <t xml:space="preserve">チャンピオンであることは誇りです。逃げずに守り抜くよ</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.normal[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.normal[2]</t>
+          <t xml:space="preserve">hallOfFame.standard.normal[1]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr" s="2">
@@ -8908,14 +8908,14 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリングで過ごした時間が、わたしの全て</t>
+          <t xml:space="preserve">後悔はない。一試合も。…本当に良い現役生活でした</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.normal[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.normal[1]</t>
+          <t xml:space="preserve">hallOfFame.standard.normal[2]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr" s="2">
@@ -8940,14 +8940,14 @@
       </c>
       <c r="F267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんな賞をいただけるなんて、びっくりです</t>
+          <t xml:space="preserve">このリングで過ごした時間が、私の全て</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.normal[1]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.normal[2]</t>
+          <t xml:space="preserve">mediaAward.standard.normal[1]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr" s="2">
@@ -8972,14 +8972,14 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リング外でも頑張った甲斐がありました</t>
+          <t xml:space="preserve">こんな賞をいただけるなんて、びっくりです</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.normal[2]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.normal[1]</t>
+          <t xml:space="preserve">mediaAward.standard.normal[2]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr" s="2">
@@ -9004,14 +9004,14 @@
       </c>
       <c r="F269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間、逃げなかった。それだけは胸を張れます</t>
+          <t xml:space="preserve">リング外でも頑張った甲斐がありました</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.normal[1]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.normal[2]</t>
+          <t xml:space="preserve">mvp.standard.normal[1]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr" s="2">
@@ -9036,14 +9036,14 @@
       </c>
       <c r="F270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">苦しい試合もあった。でも全部、今のわたしを作ってくれた</t>
+          <t xml:space="preserve">一年間、逃げなかった。それだけは胸を張れます</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.normal[2]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.normal[1]</t>
+          <t xml:space="preserve">mvp.standard.normal[2]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr" s="2">
@@ -9068,14 +9068,14 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">控室で泣きました。うれしくて。…来年はもっと上で泣きます</t>
+          <t xml:space="preserve">苦しい試合もあった。でも全部、今の私を作ってくれた</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.normal[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.normal[2]</t>
+          <t xml:space="preserve">rookie.standard.normal[1]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr" s="2">
@@ -9100,14 +9100,14 @@
       </c>
       <c r="F272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞の重さ、まだわかりません。でもリングに上がるたび、きっとわかっていくと思います</t>
+          <t xml:space="preserve">控室で泣きました。うれしくて。…来年はもっと上で泣きます</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.normal[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">rookie.standard.normal[2]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr" s="2">
@@ -9132,14 +9132,14 @@
       </c>
       <c r="F273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来られたのは、社長のおかげです</t>
+          <t xml:space="preserve">この賞の重さ、まだわかりません。でもリングに上がるたび、きっとわかっていくと思います</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.normal[1]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -9149,12 +9149,12 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">springTagChampion.standard.normal[1]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr" s="2">
@@ -9164,14 +9164,14 @@
       </c>
       <c r="F274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと、この景色を見れますね</t>
+          <t xml:space="preserve">この春を一緒に走り抜いた相棒に、まずはありがとうと言いたいです。</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr" s="2">
@@ -9196,14 +9196,14 @@
       </c>
       <c r="F275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…震えてます、正直</t>
+          <t xml:space="preserve">ここまで来られたのは、社長のおかげです</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr" s="2">
@@ -9228,14 +9228,14 @@
       </c>
       <c r="F276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員…ですか。…信じられません</t>
+          <t xml:space="preserve">やっと、この景色を見れますね</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr" s="2">
@@ -9260,14 +9260,14 @@
       </c>
       <c r="F277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長…ありがとうございます。こんな景色、見せてもらって</t>
+          <t xml:space="preserve">…震えてます、正直</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr" s="2">
@@ -9292,14 +9292,14 @@
       </c>
       <c r="F278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この光景、一生忘れません</t>
+          <t xml:space="preserve">満員…ですか。…信じられません</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.normal[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9309,29 +9309,29 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習が楽しくなってきた気がします</t>
+          <t xml:space="preserve">社長…ありがとうございます。こんな景色、見せてもらって</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.normal[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9341,29 +9341,29 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっと体が動くようになってきた気がします</t>
+          <t xml:space="preserve">この光景、一生忘れません</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.normal[1]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.normal[1]</t>
+          <t xml:space="preserve">N1.standard.normal[1]</t>
         </is>
       </c>
       <c r="E281" t="inlineStr" s="2">
@@ -9388,14 +9388,14 @@
       </c>
       <c r="F281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい仲間ができた気がします</t>
+          <t xml:space="preserve">練習が楽しくなってきた気がします</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.normal[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.normal[2]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.normal[2]</t>
+          <t xml:space="preserve">N1.standard.normal[2]</t>
         </is>
       </c>
       <c r="E282" t="inlineStr" s="2">
@@ -9420,14 +9420,14 @@
       </c>
       <c r="F282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒に頑張れる人がいると心強いですね</t>
+          <t xml:space="preserve">やっと体が動くようになってきた気がします</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.normal[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.normal[1]</t>
+          <t xml:space="preserve">N2.standard.normal[1]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr" s="2">
@@ -9452,14 +9452,14 @@
       </c>
       <c r="F283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと疲れてるだけです。次の試合までには戻ります</t>
+          <t xml:space="preserve">いい仲間ができた気がします</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.normal[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.normal[2]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.normal[2]</t>
+          <t xml:space="preserve">N2.standard.normal[2]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr" s="2">
@@ -9484,14 +9484,14 @@
       </c>
       <c r="F284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し休めば大丈夫です</t>
+          <t xml:space="preserve">一緒に頑張れる人がいると心強いですね</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.normal[1]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.normal[1]</t>
+          <t xml:space="preserve">N3.standard.normal[1]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr" s="2">
@@ -9516,14 +9516,14 @@
       </c>
       <c r="F285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなにたくさんの応援をいただけるなんて、びっくりしています</t>
+          <t xml:space="preserve">ちょっと疲れてるだけです。次の試合までには戻ります</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.normal[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.normal[2]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.normal[2]</t>
+          <t xml:space="preserve">N3.standard.normal[2]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr" s="2">
@@ -9548,14 +9548,14 @@
       </c>
       <c r="F286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの声が力になってます</t>
+          <t xml:space="preserve">少し休めば大丈夫です</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.normal[1]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.normal[1]</t>
+          <t xml:space="preserve">N4.standard.normal[1]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr" s="2">
@@ -9580,14 +9580,14 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…別に、何でもないです</t>
+          <t xml:space="preserve">こんなにたくさんの応援をいただけるなんて、びっくりしています</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.normal[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.normal[2]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.normal[2]</t>
+          <t xml:space="preserve">N4.standard.normal[2]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr" s="2">
@@ -9612,14 +9612,14 @@
       </c>
       <c r="F288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もういいです。分かりました</t>
+          <t xml:space="preserve">ファンの声が力になってます</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.normal[1]</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.standard.normal[1]</t>
+          <t xml:space="preserve">N5_low.standard.normal[1]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr" s="2">
@@ -9644,14 +9644,14 @@
       </c>
       <c r="F289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（どこか上の空で、視線が泳いでいる）</t>
+          <t xml:space="preserve">…別に、何でもないです</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.normal[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.normal[2]</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.standard.normal[2]</t>
+          <t xml:space="preserve">N5_low.standard.normal[2]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr" s="2">
@@ -9676,14 +9676,14 @@
       </c>
       <c r="F290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません、ちょっと考え事を</t>
+          <t xml:space="preserve">もういいです。分かりました</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.normal[1]</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.standard.normal[1]</t>
+          <t xml:space="preserve">N5_warning.standard.normal[1]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr" s="2">
@@ -9708,14 +9708,14 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで頑張ってきてよかった</t>
+          <t xml:space="preserve">（どこか上の空で、視線が泳いでいる）</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.normal[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.normal[2]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.standard.normal[1]</t>
+          <t xml:space="preserve">N5_warning.standard.normal[2]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr" s="2">
@@ -9740,14 +9740,14 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、こんなもんか</t>
+          <t xml:space="preserve">……すみません、ちょっと考え事を</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.normal[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.standard.normal[2]</t>
+          <t xml:space="preserve">breakthrough.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr" s="2">
@@ -9772,14 +9772,14 @@
       </c>
       <c r="F293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頑張ってるのにな</t>
+          <t xml:space="preserve">…ここで頑張ってきてよかった</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.standard.normal[1]</t>
+          <t xml:space="preserve">G1.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr" s="2">
@@ -9804,14 +9804,14 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの子、伸びたな</t>
+          <t xml:space="preserve">…まあ、こんなもんか</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.normal[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.normal[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.standard.normal[2]</t>
+          <t xml:space="preserve">G1.voice.standard.normal[2]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr" s="2">
@@ -9836,14 +9836,14 @@
       </c>
       <c r="F295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…先輩としてちゃんと見てるよ。…でもね</t>
+          <t xml:space="preserve">…頑張ってるのにな</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.standard.normal[1]</t>
+          <t xml:space="preserve">G2.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9868,14 +9868,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつになったら</t>
+          <t xml:space="preserve">…あの子、伸びたな</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.standard.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.normal[2]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.standard.normal[1]</t>
+          <t xml:space="preserve">G2.voice.standard.normal[2]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9900,14 +9900,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出番、来ないかな</t>
+          <t xml:space="preserve">…先輩としてちゃんと見てるよ。…でもね</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.standard.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.standard.normal[1]</t>
+          <t xml:space="preserve">G3.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9932,14 +9932,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、一人のほうが気楽だし</t>
+          <t xml:space="preserve">…いつになったら</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.standard.normal[1]</t>
+          <t xml:space="preserve">G4.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -9964,14 +9964,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いなくなっちゃうんだ</t>
+          <t xml:space="preserve">…出番、来ないかな</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.normal[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.standard.normal[2]</t>
+          <t xml:space="preserve">R2.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -9996,14 +9996,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{name2}がいない控え室なんて想像できない</t>
+          <t xml:space="preserve">…まあ、一人のほうが気楽だし</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.normal[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.standard.normal[1]</t>
+          <t xml:space="preserve">R3.modal.standard.normal[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -10028,14 +10028,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やっと、追いついた</t>
+          <t xml:space="preserve">…いなくなっちゃうんだ</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.normal[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.standard.normal[1]</t>
+          <t xml:space="preserve">R3.modal.standard.normal[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10060,14 +10060,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ、足りないのか</t>
+          <t xml:space="preserve">…{name2}がいない控え室なんて想像できない</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.normal[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.standard.normal[2]</t>
+          <t xml:space="preserve">R4.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10092,14 +10092,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…くやしい</t>
+          <t xml:space="preserve">…やっと、追いついた</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10109,29 +10109,29 @@
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.standard.normal[1]</t>
+          <t xml:space="preserve">R5.voice.standard.normal[1]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……これが、私の値段ですか</t>
+          <t xml:space="preserve">…まだ、足りないのか</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.normal[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.normal[2]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10141,29 +10141,29 @@
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.standard.normal[2]</t>
+          <t xml:space="preserve">R5.voice.standard.normal[2]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……お気持ちだけ、受け取っておきます</t>
+          <t xml:space="preserve">…くやしい</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.normal[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.standard.normal[1]</t>
+          <t xml:space="preserve">bonus_insult.standard.normal[1]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10188,14 +10188,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また？</t>
+          <t xml:space="preserve">……これが、私の値段ですか</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.normal[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10210,7 +10210,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.standard.normal[2]</t>
+          <t xml:space="preserve">bonus_insult.standard.normal[2]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10220,14 +10220,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっと…ありがとうございます</t>
+          <t xml:space="preserve">……お気持ちだけ、受け取っておきます</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.normal[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.normal[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.standard.normal[3]</t>
+          <t xml:space="preserve">bonus_repeat.standard.normal[1]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10252,14 +10252,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（また、お金…か…）</t>
+          <t xml:space="preserve">…また？</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.normal[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.normal[1]</t>
+          <t xml:space="preserve">bonus_repeat.standard.normal[2]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10284,14 +10284,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます！</t>
+          <t xml:space="preserve">えっと…ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.normal[3]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.normal[2]</t>
+          <t xml:space="preserve">bonus_repeat.standard.normal[3]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10316,14 +10316,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いただきます…！</t>
+          <t xml:space="preserve">（また、お金…か…）</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.normal[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.normal[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.normal[3]</t>
+          <t xml:space="preserve">bonus.standard.normal[1]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10348,14 +10348,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">感謝します</t>
+          <t xml:space="preserve">ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.normal[4]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.normal[2]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.normal[4]</t>
+          <t xml:space="preserve">bonus.standard.normal[2]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10380,14 +10380,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">励みになります！</t>
+          <t xml:space="preserve">いただきます…！</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.normal[5]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.normal[3]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.normal[5]</t>
+          <t xml:space="preserve">bonus.standard.normal[3]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10412,14 +10412,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嬉しいです！大切に使います</t>
+          <t xml:space="preserve">感謝します</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.normal[4]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.normal[1]</t>
+          <t xml:space="preserve">bonus.standard.normal[4]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
@@ -10444,14 +10444,14 @@
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり鍛えてきます！</t>
+          <t xml:space="preserve">励みになります！</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.normal[5]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.normal[2]</t>
+          <t xml:space="preserve">bonus.standard.normal[5]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
@@ -10476,14 +10476,14 @@
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頑張ります！</t>
+          <t xml:space="preserve">嬉しいです！大切に使います</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.normal[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.normal[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.normal[3]</t>
+          <t xml:space="preserve">camp.standard.normal[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10508,14 +10508,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">良い合宿にしましょう！</t>
+          <t xml:space="preserve">しっかり鍛えてきます！</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.normal[4]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.normal[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10530,7 +10530,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.normal[4]</t>
+          <t xml:space="preserve">camp.standard.normal[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10540,14 +10540,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しみです！全力で取り組みます！</t>
+          <t xml:space="preserve">頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.normal[3]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.normal[1]</t>
+          <t xml:space="preserve">camp.standard.normal[3]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10572,14 +10572,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ずっと見てくれてたんですね…頑張ります！</t>
+          <t xml:space="preserve">良い合宿にしましょう！</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.normal[4]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.normal[2]</t>
+          <t xml:space="preserve">camp.standard.normal[4]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10604,14 +10604,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたに言われると、本当に力が出ます！</t>
+          <t xml:space="preserve">楽しみです！全力で取り組みます！</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.normal[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.normal[1]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.normal[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10636,14 +10636,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…</t>
+          <t xml:space="preserve">ずっと見てくれてたんですね…頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.normal[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.normal[2]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.normal[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10668,14 +10668,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少し、頑張ってみます</t>
+          <t xml:space="preserve">あなたに言われると、本当に力が出ます！</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.normal[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.normal[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.normal[3]</t>
+          <t xml:space="preserve">encourage.standard.normal[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10700,14 +10700,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">その言葉、嬉しかったです</t>
+          <t xml:space="preserve">ありがとうございます…</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.normal[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.normal[1]</t>
+          <t xml:space="preserve">encourage.standard.normal[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10732,14 +10732,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします！</t>
+          <t xml:space="preserve">もう少し、頑張ってみます</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.normal[3]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.normal[2]</t>
+          <t xml:space="preserve">encourage.standard.normal[3]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10764,14 +10764,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます！</t>
+          <t xml:space="preserve">その言葉、嬉しかったです</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.normal[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.normal[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.normal[3]</t>
+          <t xml:space="preserve">media.standard.normal[1]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10796,14 +10796,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">緊張するけど…頑張ります！</t>
+          <t xml:space="preserve">よろしくお願いします！</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.normal[2]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.normal[1]</t>
+          <t xml:space="preserve">media.standard.normal[2]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10828,14 +10828,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お疲れ様でした〜！</t>
+          <t xml:space="preserve">ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.normal[3]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.normal[2]</t>
+          <t xml:space="preserve">media.standard.normal[3]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10860,14 +10860,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで楽しく過ごせました！</t>
+          <t xml:space="preserve">緊張するけど…頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.normal[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.normal[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.normal[3]</t>
+          <t xml:space="preserve">party.standard.normal[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10892,14 +10892,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう時間、いいですね！</t>
+          <t xml:space="preserve">お疲れ様でした〜！</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.normal[4]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.normal[2]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.normal[4]</t>
+          <t xml:space="preserve">party.standard.normal[2]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10924,14 +10924,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リフレッシュできました！</t>
+          <t xml:space="preserve">みんなで楽しく過ごせました！</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.normal[3]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.normal[1]</t>
+          <t xml:space="preserve">party.standard.normal[3]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10956,14 +10956,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます！行ってきます！</t>
+          <t xml:space="preserve">こういう時間、いいですね！</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.normal[4]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.normal[2]</t>
+          <t xml:space="preserve">party.standard.normal[4]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -10988,14 +10988,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆっくり休んで戻ってきます！</t>
+          <t xml:space="preserve">リフレッシュできました！</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.normal[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.normal[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.normal[3]</t>
+          <t xml:space="preserve">refresh_leave.standard.normal[1]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11020,14 +11020,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます…少し、休みます</t>
+          <t xml:space="preserve">ありがとうございます！行ってきます！</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.normal[2]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.normal[1]</t>
+          <t xml:space="preserve">refresh_leave.standard.normal[2]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11052,14 +11052,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">専門の先生まで…ありがとうございます。早く戻ります</t>
+          <t xml:space="preserve">ゆっくり休んで戻ってきます！</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.normal[3]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.normal[2]</t>
+          <t xml:space="preserve">refresh_leave.standard.normal[3]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11084,14 +11084,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなに気にかけていただけるなんて…必ず復帰します</t>
+          <t xml:space="preserve">ありがとうございます…少し、休みます</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.normal[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.normal[1]</t>
+          <t xml:space="preserve">special_treatment.standard.normal[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11116,14 +11116,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頑張ります！</t>
+          <t xml:space="preserve">専門の先生まで…ありがとうございます。早く戻ります</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.normal[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.normal[2]</t>
+          <t xml:space="preserve">special_treatment.standard.normal[2]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11148,14 +11148,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で取り組みます！</t>
+          <t xml:space="preserve">こんなに気にかけていただけるなんて…必ず復帰します</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.normal[3]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.normal[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.normal[3]</t>
+          <t xml:space="preserve">trainer.standard.normal[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11180,14 +11180,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しっかり吸収します！</t>
+          <t xml:space="preserve">頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.normal[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.normal[2]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11197,12 +11197,12 @@
       </c>
       <c r="C338" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.normal[1]</t>
+          <t xml:space="preserve">trainer.standard.normal[2]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11212,14 +11212,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディアへの出演、ご検討いただけますか？</t>
+          <t xml:space="preserve">全力で取り組みます！</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.normal[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.normal[3]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="C339" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.normal[2]</t>
+          <t xml:space="preserve">trainer.standard.normal[3]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11244,14 +11244,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出演のお話をいただきました。やってみたいです</t>
+          <t xml:space="preserve">しっかり吸収します！</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.normal[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E4.standard.normal[1]</t>
+          <t xml:space="preserve">E1.standard.normal[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11276,14 +11276,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新たなスカウト情報が届きました</t>
+          <t xml:space="preserve">メディアへの出演、ご検討いただけますか？</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.normal[2]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.normal[1]</t>
+          <t xml:space="preserve">E1.standard.normal[2]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11308,14 +11308,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他の団体からオファーが来ています</t>
+          <t xml:space="preserve">出演のお話をいただきました。やってみたいです</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E4.standard.normal[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.normal[1]</t>
+          <t xml:space="preserve">E4.standard.normal[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11340,14 +11340,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今日は練習する気分じゃないです</t>
+          <t xml:space="preserve">新たなスカウト情報が届きました</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.normal[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.normal[1]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.normal[2]</t>
+          <t xml:space="preserve">E6.standard.normal[1]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
@@ -11372,14 +11372,14 @@
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……すみません、今日は帰ります</t>
+          <t xml:space="preserve">他の団体からオファーが来ています</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.normal[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11394,7 +11394,7 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.standard.normal[1]</t>
+          <t xml:space="preserve">S_boycott.standard.normal[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
@@ -11404,14 +11404,14 @@
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（ロッカールームで不満を漏らしている…周囲に伝播し始めた）</t>
+          <t xml:space="preserve">……今日は練習する気分じゃないです</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.normal[2]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.standard.normal[1]</t>
+          <t xml:space="preserve">S_boycott.standard.normal[2]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11436,14 +11436,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「自分の居場所はどこなんだろう」と意味深な投稿）</t>
+          <t xml:space="preserve">……すみません、今日は帰ります</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.normal[1]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.normal[1]</t>
+          <t xml:space="preserve">S_grumble.standard.normal[1]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11468,14 +11468,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトルマッチの機会をいただけませんか？</t>
+          <t xml:space="preserve">（ロッカールームで不満を漏らしている…周囲に伝播し始めた）</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.normal[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.standard.normal[1]</t>
+          <t xml:space="preserve">S_sns.standard.normal[1]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11500,14 +11500,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">因縁のある相手と試合を組んでいただけませんか</t>
+          <t xml:space="preserve">（SNSに「自分の居場所はどこなんだろう」と意味深な投稿）</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.normal[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.standard.normal[1]</t>
+          <t xml:space="preserve">S1.standard.normal[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11532,14 +11532,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">少し休養をいただけますか？</t>
+          <t xml:space="preserve">タイトルマッチの機会をいただけませんか？</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.normal[1]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.normal[1]</t>
+          <t xml:space="preserve">S2.standard.normal[1]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11564,14 +11564,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままでは限界です。待遇を改善していただけませんか</t>
+          <t xml:space="preserve">因縁のある相手と試合を組んでいただけませんか</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.normal[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.standard.normal[1]</t>
+          <t xml:space="preserve">S3.standard.normal[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11596,14 +11596,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（沈黙）…いえ、何でもないです</t>
+          <t xml:space="preserve">少し休養をいただけますか？</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.normal[1]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.standard.normal[1]</t>
+          <t xml:space="preserve">S4_direct.standard.normal[1]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11628,14 +11628,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特訓する時間をいただけませんか？</t>
+          <t xml:space="preserve">このままでは限界です。待遇を改善していただけませんか</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.normal[1]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.standard.normal[1]</t>
+          <t xml:space="preserve">S4_silent.standard.normal[1]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11660,14 +11660,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">後輩の指導を担当させてもらえませんか？</t>
+          <t xml:space="preserve">（沈黙）…いえ、何でもないです</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.normal[1]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11677,12 +11677,12 @@
       </c>
       <c r="C353" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.standard.normal[1]</t>
+          <t xml:space="preserve">S5.standard.normal[1]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11692,14 +11692,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">出演のお話、ありがたくお受けします</t>
+          <t xml:space="preserve">特訓する時間をいただけませんか？</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.normal[1]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="C354" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.standard.normal[1]</t>
+          <t xml:space="preserve">S6.standard.normal[1]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11724,14 +11724,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えっ、わたしですか？ ……はい、頑張ります!</t>
+          <t xml:space="preserve">後輩の指導を担当させてもらえませんか？</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.normal[1]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="C355" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.standard.normal[1]</t>
+          <t xml:space="preserve">E1.accept.standard.normal[1]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11756,14 +11756,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…痛みが引くまで少し時間がかかりそうです</t>
+          <t xml:space="preserve">出演のお話、ありがたくお受けします</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.normal[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.normal[1]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11773,12 +11773,12 @@
       </c>
       <c r="C356" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.normal[1]</t>
+          <t xml:space="preserve">E1.recommend.standard.normal[1]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11788,14 +11788,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままじゃチームがもたない。何とかしてほしい</t>
+          <t xml:space="preserve">えっ、私ですか？ ……はい、頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.normal[1]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.normal[1]</t>
+          <t xml:space="preserve">B1.standard.normal[1]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11820,14 +11820,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">向こうにも非があるのに、私だけ悪いみたいに…</t>
+          <t xml:space="preserve">…痛みが引くまで少し時間がかかりそうです</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.normal[1]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.normal[1]</t>
+          <t xml:space="preserve">B2_fighter1.standard.normal[1]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11852,14 +11852,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ブランドとのコラボか。ちゃんとイメージに合わせられるかな</t>
+          <t xml:space="preserve">このままじゃチームがもたない。何とかしてほしい</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.normal[1]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.normal[1]</t>
+          <t xml:space="preserve">B2_fighter2.standard.normal[1]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11884,14 +11884,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CMか…ちゃんとできるかな。頑張ってみます</t>
+          <t xml:space="preserve">向こうにも非があるのに、私だけ悪いみたいに…</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.normal[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.normal[1]</t>
+          <t xml:space="preserve">B4_brand.standard.normal[1]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11916,14 +11916,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンの皆さんと直接話せるのか。楽しみです</t>
+          <t xml:space="preserve">ブランドとのコラボか。ちゃんとイメージに合わせられるかな</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.normal[1]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.normal[1]</t>
+          <t xml:space="preserve">B4_cm.standard.normal[1]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11948,14 +11948,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファッションショーか…歩けるかな。頑張ります</t>
+          <t xml:space="preserve">CMか…ちゃんとできるかな。頑張ってみます</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.normal[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.normal[1]</t>
+          <t xml:space="preserve">B4_fan.standard.normal[1]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -11980,14 +11980,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">グラビアか…ちょっと恥ずかしいけど、頑張ります</t>
+          <t xml:space="preserve">ファンの皆さんと直接話せるのか。楽しみです</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.normal[1]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.normal[1]</t>
+          <t xml:space="preserve">B4_fashion.standard.normal[1]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -12012,14 +12012,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">バラエティか…うまく喋れるかな。頑張ります</t>
+          <t xml:space="preserve">ファッションショーか…歩けるかな。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.normal[1]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.normal[1]</t>
+          <t xml:space="preserve">B4_gravure.standard.normal[1]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -12044,14 +12044,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">取材…緊張しますが、いい試合を見せられるよう頑張ります</t>
+          <t xml:space="preserve">グラビアか…ちょっと恥ずかしいけど、頑張ります</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.normal[1]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -12061,29 +12061,29 @@
       </c>
       <c r="C365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">B4_variety.standard.normal[1]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします。精一杯やります</t>
+          <t xml:space="preserve">バラエティか…うまく喋れるかな。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.normal[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -12093,29 +12093,29 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">B4.standard.normal[1]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけたら、全力で頑張ります</t>
+          <t xml:space="preserve">取材…緊張しますが、いい試合を見せられるよう頑張ります</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="12">
@@ -12140,14 +12140,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします。精一杯頑張ります</t>
+          <t xml:space="preserve">よろしくお願いします。精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="C368" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D368" t="inlineStr" s="12">
@@ -12172,14 +12172,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくださって、ありがとうございます</t>
+          <t xml:space="preserve">選んでいただけたら、全力で頑張ります</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12204,14 +12204,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、頑張ります</t>
+          <t xml:space="preserve">よろしくお願いします。精一杯頑張ります</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12221,12 +12221,12 @@
       </c>
       <c r="C370" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -12236,14 +12236,14 @@
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします。力になれるよう頑張ります</t>
+          <t xml:space="preserve">選んでくださって、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="C371" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -12268,14 +12268,14 @@
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい環境…悪くないですね。頑張ります</t>
+          <t xml:space="preserve">期待に応えられるよう、頑張ります</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C372" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D372" t="inlineStr" s="12">
@@ -12300,14 +12300,14 @@
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします。頑張ります</t>
+          <t xml:space="preserve">よろしくお願いします。力になれるよう頑張ります</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="C373" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D373" t="inlineStr" s="12">
@@ -12332,14 +12332,14 @@
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力になれるよう、精一杯やります</t>
+          <t xml:space="preserve">新しい環境…悪くないですね。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="C374" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D374" t="inlineStr" s="12">
@@ -12364,14 +12364,14 @@
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅ…痛い…。でも、すぐ戻ります</t>
+          <t xml:space="preserve">よろしくお願いします。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="C375" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D375" t="inlineStr" s="12">
@@ -12396,14 +12396,14 @@
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しばらくお休みをいただきます</t>
+          <t xml:space="preserve">力になれるよう、精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12428,14 +12428,14 @@
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…体が言うことを聞かなくて</t>
+          <t xml:space="preserve">うぅ…痛い…。でも、すぐ戻ります</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="C377" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
@@ -12460,14 +12460,14 @@
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったはずなのに、まだ胃の底が重い</t>
+          <t xml:space="preserve">しばらくお休みをいただきます</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12477,12 +12477,12 @@
       </c>
       <c r="C378" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D378" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12492,14 +12492,14 @@
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう一度勝てば消えるのかな。……多分、消えない</t>
+          <t xml:space="preserve">ごめんなさい…体が言うことを聞かなくて</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.normal[1]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.normal[1]</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12524,14 +12524,14 @@
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わったことにされた。私だけ、置いていかれたまま</t>
+          <t xml:space="preserve">終わったはずなのに、まだ胃の底が重い</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.normal[2]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.normal[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.normal[2]</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12556,14 +12556,14 @@
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">忘れられたら楽だったのに。……よく覚えてるんだ、これが</t>
+          <t xml:space="preserve">もう一度勝てば消えるのかな。……多分、消えない</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.normal[1]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.normal[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.normal[1]</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12588,14 +12588,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします。精一杯やります</t>
+          <t xml:space="preserve">終わったことにされた。私だけ、置いていかれたまま</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.normal[2]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.normal[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.normal[2]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12620,14 +12620,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでいただけたら、全力で頑張ります</t>
+          <t xml:space="preserve">忘れられたら楽だったのに。……よく覚えてるんだ、これが</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.normal[1]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.normal[1]</t>
+          <t xml:space="preserve">draftInterest.standard.normal[1]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12652,14 +12652,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします。精一杯頑張ります</t>
+          <t xml:space="preserve">よろしくお願いします。精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.normal[2]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.normal[2]</t>
+          <t xml:space="preserve">draftInterest.standard.normal[2]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12684,14 +12684,14 @@
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選んでくださって、ありがとうございます</t>
+          <t xml:space="preserve">選んでいただけたら、全力で頑張ります</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.normal[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.normal[1]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.normal[3]</t>
+          <t xml:space="preserve">draftJoin.standard.normal[1]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12716,14 +12716,14 @@
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待に応えられるよう、頑張ります</t>
+          <t xml:space="preserve">よろしくお願いします。精一杯頑張ります</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.normal[2]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.normal[1]</t>
+          <t xml:space="preserve">draftJoin.standard.normal[2]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12748,14 +12748,14 @@
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">所属が決まるって、やっぱり落ち着くね</t>
+          <t xml:space="preserve">選んでくださって、ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.normal[3]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.normal[2]</t>
+          <t xml:space="preserve">draftJoin.standard.normal[3]</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
@@ -12780,14 +12780,14 @@
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また声がかかって嬉しいよ。今度は長くいたいね</t>
+          <t xml:space="preserve">期待に応えられるよう、頑張ります</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.normal[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.normal[1]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.normal[3]</t>
+          <t xml:space="preserve">faGreeting.standard.normal[1]</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12812,14 +12812,14 @@
       </c>
       <c r="F388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーも気楽だったけど、やっぱりリングが一番だね</t>
+          <t xml:space="preserve">所属が決まるって、やっぱり落ち着くね</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.normal[2]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.normal[1]</t>
+          <t xml:space="preserve">faGreeting.standard.normal[2]</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12844,14 +12844,14 @@
       </c>
       <c r="F389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします。力になれるよう頑張ります</t>
+          <t xml:space="preserve">また声がかかって嬉しいよ。今度は長くいたいね</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.normal[3]</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="D390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.normal[2]</t>
+          <t xml:space="preserve">faGreeting.standard.normal[3]</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12876,14 +12876,14 @@
       </c>
       <c r="F390" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい環境…悪くないですね。頑張ります</t>
+          <t xml:space="preserve">フリーも気楽だったけど、やっぱりリングが一番だね</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.normal[1]</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="D391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.normal[1]</t>
+          <t xml:space="preserve">faSigning.standard.normal[1]</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12908,14 +12908,14 @@
       </c>
       <c r="F391" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします。頑張ります</t>
+          <t xml:space="preserve">よろしくお願いします。力になれるよう頑張ります</t>
         </is>
       </c>
     </row>
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.normal[2]</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="D392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.normal[2]</t>
+          <t xml:space="preserve">faSigning.standard.normal[2]</t>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -12940,14 +12940,14 @@
       </c>
       <c r="F392" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力になれるよう、精一杯やります</t>
+          <t xml:space="preserve">新しい環境…悪くないですね。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.normal[1]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.standard.normal[1]</t>
+          <t xml:space="preserve">faWelcome.standard.normal[1]</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -12972,14 +12972,14 @@
       </c>
       <c r="F393" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は体が軽い。なんでもできそうな気がする</t>
+          <t xml:space="preserve">よろしくお願いします。頑張ります</t>
         </is>
       </c>
     </row>
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.normal[2]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.standard.normal[1]</t>
+          <t xml:space="preserve">faWelcome.standard.normal[2]</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -13004,14 +13004,14 @@
       </c>
       <c r="F394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が重い。動いてはいるけど、何も残らないな</t>
+          <t xml:space="preserve">力になれるよう、精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.normal[1]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.standard.normal[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.standard.normal[1]</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -13036,14 +13036,14 @@
       </c>
       <c r="F395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じだけやってるのに、手応えが薄い気がする</t>
+          <t xml:space="preserve">今日は体が軽い。なんでもできそうな気がする</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.normal[1]</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="D396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.normal[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.standard.normal[1]</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -13068,14 +13068,14 @@
       </c>
       <c r="F396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うぅ…痛い…。でも、すぐ戻ります</t>
+          <t xml:space="preserve">体が重い。動いてはいるけど、何も残らないな</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.normal[1]</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="D397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.normal[2]</t>
+          <t xml:space="preserve">heatSelf.warm.standard.normal[1]</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -13100,14 +13100,14 @@
       </c>
       <c r="F397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">しばらくお休みをいただきます</t>
+          <t xml:space="preserve">同じだけやってるのに、手応えが薄い気がする</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.normal[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.normal[1]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.normal[3]</t>
+          <t xml:space="preserve">injury.standard.normal[1]</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -13132,14 +13132,14 @@
       </c>
       <c r="F398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい…体が言うことを聞かなくて</t>
+          <t xml:space="preserve">うぅ…痛い…。でも、すぐ戻ります</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.normal[2]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.normal[1]</t>
+          <t xml:space="preserve">injury.standard.normal[2]</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -13164,14 +13164,14 @@
       </c>
       <c r="F399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そう…ですか。ここでの思い出、忘れません</t>
+          <t xml:space="preserve">しばらくお休みをいただきます</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.normal[3]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.normal[2]</t>
+          <t xml:space="preserve">injury.standard.normal[3]</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -13196,14 +13196,14 @@
       </c>
       <c r="F400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました…</t>
+          <t xml:space="preserve">ごめんなさい…体が言うことを聞かなくて</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.normal[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.normal[1]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="D401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.normal[3]</t>
+          <t xml:space="preserve">release.standard.normal[1]</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -13228,14 +13228,14 @@
       </c>
       <c r="F401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…でも、ありがとうございました</t>
+          <t xml:space="preserve">そう…ですか。ここでの思い出、忘れません</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.normal[2]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="D402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.normal[1]</t>
+          <t xml:space="preserve">release.standard.normal[2]</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -13260,14 +13260,14 @@
       </c>
       <c r="F402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルですが、手は抜きませんので。よろしく</t>
+          <t xml:space="preserve">お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.normal[3]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="D403" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.normal[2]</t>
+          <t xml:space="preserve">release.standard.normal[3]</t>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -13292,14 +13292,14 @@
       </c>
       <c r="F403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですがよろしくお願いします</t>
+          <t xml:space="preserve">悔しいです…でも、ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.normal[1]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="D404" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.normal[1]</t>
+          <t xml:space="preserve">rentalGreeting.standard.normal[1]</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -13324,14 +13324,14 @@
       </c>
       <c r="F404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくれた目を信じて、頑張ってみるね</t>
+          <t xml:space="preserve">レンタルですが、手は抜きませんので。よろしく</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.normal[2]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="D405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.normal[2]</t>
+          <t xml:space="preserve">rentalGreeting.standard.normal[2]</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13356,14 +13356,14 @@
       </c>
       <c r="F405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさか自分に声がかかるとはね。よろしく</t>
+          <t xml:space="preserve">短い間ですがよろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.normal[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.normal[1]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="D406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.normal[3]</t>
+          <t xml:space="preserve">scoutGreeting.standard.normal[1]</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13388,14 +13388,14 @@
       </c>
       <c r="F406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待されてるうちに、いいとこ見せないとね</t>
+          <t xml:space="preserve">声をかけてくれた目を信じて、頑張ってみるね</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.normal[2]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.normal[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.normal[2]</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
@@ -13420,14 +13420,14 @@
       </c>
       <c r="F407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…。でも、いい経験になりました。次こそは…！</t>
+          <t xml:space="preserve">まさか自分に声がかかるとはね。よろしく</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.normal[3]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.normal[2]</t>
+          <t xml:space="preserve">scoutGreeting.standard.normal[3]</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
@@ -13452,14 +13452,14 @@
       </c>
       <c r="F408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ実力が足りなかった…。もっと強くなって帰ってきます。</t>
+          <t xml:space="preserve">期待されてるうちに、いいとこ見せないとね</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.normal[1]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -13474,7 +13474,7 @@
       </c>
       <c r="D409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.normal[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.normal[1]</t>
         </is>
       </c>
       <c r="E409" t="inlineStr" s="2">
@@ -13484,14 +13484,14 @@
       </c>
       <c r="F409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛成功…！ほっとした…。でも、もっと強くならないと。</t>
+          <t xml:space="preserve">悔しい…。でも、いい経験になりました。次こそは…！</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.normal[2]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="D410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.normal[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.normal[2]</t>
         </is>
       </c>
       <c r="E410" t="inlineStr" s="2">
@@ -13516,14 +13516,14 @@
       </c>
       <c r="F410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトの重さ、守るたびに感じます。</t>
+          <t xml:space="preserve">まだ実力が足りなかった…。もっと強くなって帰ってきます。</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.normal[1]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13538,7 +13538,7 @@
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.normal[1]</t>
+          <t xml:space="preserve">titleDefense.standard.normal[1]</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13548,14 +13548,14 @@
       </c>
       <c r="F411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失ってしまった…。でも、この団体で戦い続けます。</t>
+          <t xml:space="preserve">防衛成功…！ほっとした…。でも、もっと強くならないと。</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.normal[2]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.normal[2]</t>
+          <t xml:space="preserve">titleDefense.standard.normal[2]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13580,14 +13580,14 @@
       </c>
       <c r="F412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。チャンピオンとしてもっとやれたはずなのに。</t>
+          <t xml:space="preserve">このベルトの重さ、守るたびに感じます。</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.normal[1]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.normal[1]</t>
+          <t xml:space="preserve">titleLoss.standard.normal[1]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13612,14 +13612,14 @@
       </c>
       <c r="F413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった…！チャンピオンになれた…！夢みたい！</t>
+          <t xml:space="preserve">ベルトを失ってしまった…。でも、この団体で戦い続けます。</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.normal[2]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.normal[2]</t>
+          <t xml:space="preserve">titleLoss.standard.normal[2]</t>
         </is>
       </c>
       <c r="E414" t="inlineStr" s="2">
@@ -13644,14 +13644,14 @@
       </c>
       <c r="F414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト、絶対に手放しません！</t>
+          <t xml:space="preserve">…悔しい。チャンピオンとしてもっとやれたはずなのに。</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.normal[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.normal[3]</t>
+          <t xml:space="preserve">titleWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="E415" t="inlineStr" s="2">
@@ -13676,14 +13676,14 @@
       </c>
       <c r="F415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の気分です！応援ありがとうございます！</t>
+          <t xml:space="preserve">やった…！チャンピオンになれた…！夢みたい！</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13693,12 +13693,12 @@
       </c>
       <c r="C416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D416" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">titleWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="E416" t="inlineStr" s="2">
@@ -13708,14 +13708,14 @@
       </c>
       <c r="F416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そう…ですか。ここでの思い出、忘れません</t>
+          <t xml:space="preserve">このベルト、絶対に手放しません！</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.normal[3]</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="C417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D417" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">titleWin.standard.normal[3]</t>
         </is>
       </c>
       <c r="E417" t="inlineStr" s="2">
@@ -13740,14 +13740,14 @@
       </c>
       <c r="F417" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お世話になりました…</t>
+          <t xml:space="preserve">最高の気分です！応援ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="418" ht="40" customHeight="1">
       <c r="A418" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="D418" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13772,14 +13772,14 @@
       </c>
       <c r="F418" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいです…でも、ありがとうございました</t>
+          <t xml:space="preserve">そう…ですか。ここでの思い出、忘れません</t>
         </is>
       </c>
     </row>
     <row r="419" ht="40" customHeight="1">
       <c r="A419" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -13789,12 +13789,12 @@
       </c>
       <c r="C419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D419" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13804,14 +13804,14 @@
       </c>
       <c r="F419" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルですが、手は抜きませんので。よろしく</t>
+          <t xml:space="preserve">お世話になりました…</t>
         </is>
       </c>
     </row>
     <row r="420" ht="40" customHeight="1">
       <c r="A420" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -13821,12 +13821,12 @@
       </c>
       <c r="C420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D420" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13836,14 +13836,14 @@
       </c>
       <c r="F420" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">短い間ですがよろしくお願いします</t>
+          <t xml:space="preserve">悔しいです…でも、ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="421" ht="40" customHeight="1">
       <c r="A421" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="C421" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D421" t="inlineStr" s="12">
@@ -13868,14 +13868,14 @@
       </c>
       <c r="F421" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…。でも、いい経験になりました。次こそは…！</t>
+          <t xml:space="preserve">レンタルですが、手は抜きませんので。よろしく</t>
         </is>
       </c>
     </row>
     <row r="422" ht="40" customHeight="1">
       <c r="A422" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
@@ -13885,7 +13885,7 @@
       </c>
       <c r="C422" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D422" t="inlineStr" s="12">
@@ -13900,14 +13900,14 @@
       </c>
       <c r="F422" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ実力が足りなかった…。もっと強くなって帰ってきます。</t>
+          <t xml:space="preserve">短い間ですがよろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="423" ht="40" customHeight="1">
       <c r="A423" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="C423" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D423" t="inlineStr" s="12">
@@ -13932,14 +13932,14 @@
       </c>
       <c r="F423" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛成功…！ほっとした…。でも、もっと強くならないと。</t>
+          <t xml:space="preserve">悔しい…。でも、いい経験になりました。次こそは…！</t>
         </is>
       </c>
     </row>
     <row r="424" ht="40" customHeight="1">
       <c r="A424" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="C424" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D424" t="inlineStr" s="12">
@@ -13964,14 +13964,14 @@
       </c>
       <c r="F424" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルトの重さ、守るたびに感じます。</t>
+          <t xml:space="preserve">まだ実力が足りなかった…。もっと強くなって帰ってきます。</t>
         </is>
       </c>
     </row>
     <row r="425" ht="40" customHeight="1">
       <c r="A425" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="C425" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D425" t="inlineStr" s="12">
@@ -13996,14 +13996,14 @@
       </c>
       <c r="F425" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失ってしまった…。でも、この団体で戦い続けます。</t>
+          <t xml:space="preserve">防衛成功…！ほっとした…。でも、もっと強くならないと。</t>
         </is>
       </c>
     </row>
     <row r="426" ht="40" customHeight="1">
       <c r="A426" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="C426" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D426" t="inlineStr" s="12">
@@ -14028,14 +14028,14 @@
       </c>
       <c r="F426" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい。チャンピオンとしてもっとやれたはずなのに。</t>
+          <t xml:space="preserve">このベルトの重さ、守るたびに感じます。</t>
         </is>
       </c>
     </row>
     <row r="427" ht="40" customHeight="1">
       <c r="A427" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="C427" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D427" t="inlineStr" s="12">
@@ -14060,14 +14060,14 @@
       </c>
       <c r="F427" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった…！チャンピオンになれた…！夢みたい！</t>
+          <t xml:space="preserve">ベルトを失ってしまった…。でも、この団体で戦い続けます。</t>
         </is>
       </c>
     </row>
     <row r="428" ht="40" customHeight="1">
       <c r="A428" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
@@ -14077,7 +14077,7 @@
       </c>
       <c r="C428" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D428" t="inlineStr" s="12">
@@ -14092,14 +14092,14 @@
       </c>
       <c r="F428" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このベルト、絶対に手放しません！</t>
+          <t xml:space="preserve">…悔しい。チャンピオンとしてもっとやれたはずなのに。</t>
         </is>
       </c>
     </row>
     <row r="429" ht="40" customHeight="1">
       <c r="A429" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="D429" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E429" t="inlineStr" s="2">
@@ -14124,14 +14124,14 @@
       </c>
       <c r="F429" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の気分です！応援ありがとうございます！</t>
+          <t xml:space="preserve">やった…！チャンピオンになれた…！夢みたい！</t>
         </is>
       </c>
     </row>
     <row r="430" ht="40" customHeight="1">
       <c r="A430" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
@@ -14141,29 +14141,29 @@
       </c>
       <c r="C430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D430" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.standard[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E430" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F430" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もうダメかもしれない</t>
+          <t xml:space="preserve">このベルト、絶対に手放しません！</t>
         </is>
       </c>
     </row>
     <row r="431" ht="40" customHeight="1">
       <c r="A431" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.standard[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
@@ -14173,29 +14173,29 @@
       </c>
       <c r="C431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D431" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.normal.standard[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E431" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F431" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">顔を合わせるだけで気まずい</t>
+          <t xml:space="preserve">最高の気分です！応援ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="432" ht="40" customHeight="1">
       <c r="A432" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.standard[1]</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="D432" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.standard[1]</t>
+          <t xml:space="preserve">bond_39_down.normal.standard[1]</t>
         </is>
       </c>
       <c r="E432" t="inlineStr" s="2">
@@ -14220,14 +14220,14 @@
       </c>
       <c r="F432" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、目が合わなくなった気がする</t>
+          <t xml:space="preserve">…もうダメかもしれない</t>
         </is>
       </c>
     </row>
     <row r="433" ht="40" customHeight="1">
       <c r="A433" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.normal.standard[2]</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="D433" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.normal.standard[2]</t>
+          <t xml:space="preserve">bond_39_down.normal.standard[2]</t>
         </is>
       </c>
       <c r="E433" t="inlineStr" s="2">
@@ -14252,14 +14252,14 @@
       </c>
       <c r="F433" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">距離…少し開いたかも</t>
+          <t xml:space="preserve">顔を合わせるだけで気まずい</t>
         </is>
       </c>
     </row>
     <row r="434" ht="40" customHeight="1">
       <c r="A434" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.standard[1]</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="D434" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.standard[1]</t>
+          <t xml:space="preserve">bond_59_down.normal.standard[1]</t>
         </is>
       </c>
       <c r="E434" t="inlineStr" s="2">
@@ -14284,14 +14284,14 @@
       </c>
       <c r="F434" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、一緒にいるとなんだか居心地がいい気がする</t>
+          <t xml:space="preserve">最近、目が合わなくなった気がする</t>
         </is>
       </c>
     </row>
     <row r="435" ht="40" customHeight="1">
       <c r="A435" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.normal.standard[2]</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="D435" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.normal.standard[2]</t>
+          <t xml:space="preserve">bond_59_down.normal.standard[2]</t>
         </is>
       </c>
       <c r="E435" t="inlineStr" s="2">
@@ -14316,14 +14316,14 @@
       </c>
       <c r="F435" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">不思議と気が合う。一緒にいて楽なのよね</t>
+          <t xml:space="preserve">距離…少し開いたかも</t>
         </is>
       </c>
     </row>
     <row r="436" ht="40" customHeight="1">
       <c r="A436" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.standard[1]</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="D436" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.standard[1]</t>
+          <t xml:space="preserve">bond_60_up.normal.standard[1]</t>
         </is>
       </c>
       <c r="E436" t="inlineStr" s="2">
@@ -14348,14 +14348,14 @@
       </c>
       <c r="F436" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう仲間とかそういう言葉じゃ足りない。大事な存在。</t>
+          <t xml:space="preserve">最近、一緒にいるとなんだか居心地がいい気がする</t>
         </is>
       </c>
     </row>
     <row r="437" ht="40" customHeight="1">
       <c r="A437" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.normal.standard[2]</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
@@ -14370,7 +14370,7 @@
       </c>
       <c r="D437" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.normal.standard[2]</t>
+          <t xml:space="preserve">bond_60_up.normal.standard[2]</t>
         </is>
       </c>
       <c r="E437" t="inlineStr" s="2">
@@ -14380,14 +14380,14 @@
       </c>
       <c r="F437" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人がいるから、ここにいる意味がある</t>
+          <t xml:space="preserve">不思議と気が合う。一緒にいて楽なのよね</t>
         </is>
       </c>
     </row>
     <row r="438" ht="40" customHeight="1">
       <c r="A438" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.standard[1]</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="D438" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.standard[1]</t>
+          <t xml:space="preserve">bond_80_up.normal.standard[1]</t>
         </is>
       </c>
       <c r="E438" t="inlineStr" s="2">
@@ -14412,14 +14412,14 @@
       </c>
       <c r="F438" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">前ほど意識しなくなったかもしれない</t>
+          <t xml:space="preserve">もう仲間とかそういう言葉じゃ足りない。大事な存在。</t>
         </is>
       </c>
     </row>
     <row r="439" ht="40" customHeight="1">
       <c r="A439" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.normal.standard[2]</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="D439" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.normal.standard[2]</t>
+          <t xml:space="preserve">bond_80_up.normal.standard[2]</t>
         </is>
       </c>
       <c r="E439" t="inlineStr" s="2">
@@ -14444,14 +14444,14 @@
       </c>
       <c r="F439" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの因縁も…もう終わったのかな</t>
+          <t xml:space="preserve">この人がいるから、ここにいる意味がある</t>
         </is>
       </c>
     </row>
     <row r="440" ht="40" customHeight="1">
       <c r="A440" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.standard[1]</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="D440" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.standard[1]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.standard[1]</t>
         </is>
       </c>
       <c r="E440" t="inlineStr" s="2">
@@ -14476,14 +14476,14 @@
       </c>
       <c r="F440" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…最近やたら気になる。負けたくない</t>
+          <t xml:space="preserve">前ほど意識しなくなったかもしれない</t>
         </is>
       </c>
     </row>
     <row r="441" ht="40" customHeight="1">
       <c r="A441" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.normal.standard[2]</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="D441" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.normal.standard[2]</t>
+          <t xml:space="preserve">rivalry_29_down.normal.standard[2]</t>
         </is>
       </c>
       <c r="E441" t="inlineStr" s="2">
@@ -14508,14 +14508,14 @@
       </c>
       <c r="F441" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても…意識してしまう</t>
+          <t xml:space="preserve">あの因縁も…もう終わったのかな</t>
         </is>
       </c>
     </row>
     <row r="442" ht="40" customHeight="1">
       <c r="A442" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.standard[1]</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="D442" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.standard[1]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.standard[1]</t>
         </is>
       </c>
       <c r="E442" t="inlineStr" s="2">
@@ -14540,14 +14540,14 @@
       </c>
       <c r="F442" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶対に負けられない。絶対に</t>
+          <t xml:space="preserve">…最近やたら気になる。負けたくない</t>
         </is>
       </c>
     </row>
     <row r="443" ht="40" customHeight="1">
       <c r="A443" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.normal.standard[2]</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
@@ -14562,7 +14562,7 @@
       </c>
       <c r="D443" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.normal.standard[2]</t>
+          <t xml:space="preserve">rivalry_30_up.normal.standard[2]</t>
         </is>
       </c>
       <c r="E443" t="inlineStr" s="2">
@@ -14572,14 +14572,14 @@
       </c>
       <c r="F443" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">名前を聞くだけで拳が握りしまる</t>
+          <t xml:space="preserve">どうしても…意識してしまう</t>
         </is>
       </c>
     </row>
     <row r="444" ht="40" customHeight="1">
       <c r="A444" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.standard[1]</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="D444" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.standard[1]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.standard[1]</t>
         </is>
       </c>
       <c r="E444" t="inlineStr" s="2">
@@ -14604,14 +14604,14 @@
       </c>
       <c r="F444" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう運命みたいなものだと思ってる</t>
+          <t xml:space="preserve">絶対に負けられない。絶対に</t>
         </is>
       </c>
     </row>
     <row r="445" ht="40" customHeight="1">
       <c r="A445" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.normal.standard[2]</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="D445" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.normal.standard[2]</t>
+          <t xml:space="preserve">rivalry_50_up.normal.standard[2]</t>
         </is>
       </c>
       <c r="E445" t="inlineStr" s="2">
@@ -14636,14 +14636,14 @@
       </c>
       <c r="F445" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この存在がなかったら、今の自分はいない</t>
+          <t xml:space="preserve">名前を聞くだけで、拳に力がこもる</t>
         </is>
       </c>
     </row>
     <row r="446" ht="40" customHeight="1">
       <c r="A446" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.standard[1]</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="D446" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.standard[1]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.standard[1]</t>
         </is>
       </c>
       <c r="E446" t="inlineStr" s="2">
@@ -14668,14 +14668,14 @@
       </c>
       <c r="F446" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体に来てよかった。ここが自分の居場所だ</t>
+          <t xml:space="preserve">もう運命みたいなものだと思ってる</t>
         </is>
       </c>
     </row>
     <row r="447" ht="40" customHeight="1">
       <c r="A447" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.normal.standard[2]</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="2">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="D447" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.normal.standard[2]</t>
+          <t xml:space="preserve">rivalry_70_up.normal.standard[2]</t>
         </is>
       </c>
       <c r="E447" t="inlineStr" s="2">
@@ -14700,14 +14700,14 @@
       </c>
       <c r="F447" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと一緒にもっと上を目指したい</t>
+          <t xml:space="preserve">この存在がなかったら、今の自分はいない</t>
         </is>
       </c>
     </row>
     <row r="448" ht="40" customHeight="1">
       <c r="A448" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.standard[1]</t>
         </is>
       </c>
       <c r="B448" t="inlineStr" s="2">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="D448" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.standard[1]</t>
+          <t xml:space="preserve">trust_above_75.normal.standard[1]</t>
         </is>
       </c>
       <c r="E448" t="inlineStr" s="2">
@@ -14732,14 +14732,14 @@
       </c>
       <c r="F448" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう限界かもしれない。ここにいる理由が見つからない</t>
+          <t xml:space="preserve">この団体に来てよかった。ここが自分の居場所だ</t>
         </is>
       </c>
     </row>
     <row r="449" ht="40" customHeight="1">
       <c r="A449" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.normal.standard[2]</t>
         </is>
       </c>
       <c r="B449" t="inlineStr" s="2">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="D449" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.normal.standard[2]</t>
+          <t xml:space="preserve">trust_above_75.normal.standard[2]</t>
         </is>
       </c>
       <c r="E449" t="inlineStr" s="2">
@@ -14764,14 +14764,14 @@
       </c>
       <c r="F449" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…他の団体のことを、考え始めてしまっている</t>
+          <t xml:space="preserve">みんなと一緒にもっと上を目指したい</t>
         </is>
       </c>
     </row>
     <row r="450" ht="40" customHeight="1">
       <c r="A450" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.standard[1]</t>
         </is>
       </c>
       <c r="B450" t="inlineStr" s="2">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="D450" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.standard[1]</t>
+          <t xml:space="preserve">trust_below_20.normal.standard[1]</t>
         </is>
       </c>
       <c r="E450" t="inlineStr" s="2">
@@ -14796,14 +14796,14 @@
       </c>
       <c r="F450" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体で…本当にやっていけるのかな</t>
+          <t xml:space="preserve">もう限界かもしれない。ここにいる理由が見つからない</t>
         </is>
       </c>
     </row>
     <row r="451" ht="40" customHeight="1">
       <c r="A451" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.normal.standard[2]</t>
         </is>
       </c>
       <c r="B451" t="inlineStr" s="2">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="D451" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.normal.standard[2]</t>
+          <t xml:space="preserve">trust_below_20.normal.standard[2]</t>
         </is>
       </c>
       <c r="E451" t="inlineStr" s="2">
@@ -14828,14 +14828,14 @@
       </c>
       <c r="F451" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">自分のこと、ちゃんと見てくれてるのかな…</t>
+          <t xml:space="preserve">…他の団体のことを、考え始めてしまっている</t>
         </is>
       </c>
     </row>
     <row r="452" ht="40" customHeight="1">
       <c r="A452" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.standard[1]</t>
         </is>
       </c>
       <c r="B452" t="inlineStr" s="2">
@@ -14845,12 +14845,12 @@
       </c>
       <c r="C452" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D452" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.normal[1]</t>
+          <t xml:space="preserve">trust_below_35.normal.standard[1]</t>
         </is>
       </c>
       <c r="E452" t="inlineStr" s="2">
@@ -14860,14 +14860,14 @@
       </c>
       <c r="F452" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど…いい試合だった。得るものはあった</t>
+          <t xml:space="preserve">この団体で…本当にやっていけるのかな</t>
         </is>
       </c>
     </row>
     <row r="453" ht="40" customHeight="1">
       <c r="A453" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.normal.standard[2]</t>
         </is>
       </c>
       <c r="B453" t="inlineStr" s="2">
@@ -14877,12 +14877,12 @@
       </c>
       <c r="C453" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D453" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.normal[2]</t>
+          <t xml:space="preserve">trust_below_35.normal.standard[2]</t>
         </is>
       </c>
       <c r="E453" t="inlineStr" s="2">
@@ -14892,14 +14892,14 @@
       </c>
       <c r="F453" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど、あの人は強かった。認めるしかない</t>
+          <t xml:space="preserve">自分のこと、ちゃんと見てくれてるのかな…</t>
         </is>
       </c>
     </row>
     <row r="454" ht="40" customHeight="1">
       <c r="A454" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.normal[1]</t>
         </is>
       </c>
       <c r="B454" t="inlineStr" s="2">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="D454" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.normal[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.normal[1]</t>
         </is>
       </c>
       <c r="E454" t="inlineStr" s="2">
@@ -14924,14 +14924,14 @@
       </c>
       <c r="F454" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合で勝てた…！ この感覚を忘れない</t>
+          <t xml:space="preserve">負けたけど…いい試合だった。得るものはあった</t>
         </is>
       </c>
     </row>
     <row r="455" ht="40" customHeight="1">
       <c r="A455" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.normal[2]</t>
         </is>
       </c>
       <c r="B455" t="inlineStr" s="2">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="D455" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.normal[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.normal[2]</t>
         </is>
       </c>
       <c r="E455" t="inlineStr" s="2">
@@ -14956,14 +14956,14 @@
       </c>
       <c r="F455" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は自分でも驚くくらいいい試合ができた</t>
+          <t xml:space="preserve">悔しいけど、あの人は強かった。認めるしかない</t>
         </is>
       </c>
     </row>
     <row r="456" ht="40" customHeight="1">
       <c r="A456" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="B456" t="inlineStr" s="2">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="D456" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.normal[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="E456" t="inlineStr" s="2">
@@ -14988,14 +14988,14 @@
       </c>
       <c r="F456" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた…。悔しい</t>
+          <t xml:space="preserve">最高の試合で勝てた…！ この感覚を忘れない</t>
         </is>
       </c>
     </row>
     <row r="457" ht="40" customHeight="1">
       <c r="A457" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="B457" t="inlineStr" s="2">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="D457" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.normal[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="E457" t="inlineStr" s="2">
@@ -15020,14 +15020,14 @@
       </c>
       <c r="F457" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は相手が上だった。次は負けない</t>
+          <t xml:space="preserve">今日は自分でも驚くくらいいい試合ができた</t>
         </is>
       </c>
     </row>
     <row r="458" ht="40" customHeight="1">
       <c r="A458" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.normal[1]</t>
         </is>
       </c>
       <c r="B458" t="inlineStr" s="2">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="D458" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.normal[1]</t>
+          <t xml:space="preserve">GL-01.loss.standard.normal[1]</t>
         </is>
       </c>
       <c r="E458" t="inlineStr" s="2">
@@ -15052,14 +15052,14 @@
       </c>
       <c r="F458" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よし、勝てた。この調子で頑張ろう</t>
+          <t xml:space="preserve">負けた…。悔しい</t>
         </is>
       </c>
     </row>
     <row r="459" ht="40" customHeight="1">
       <c r="A459" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.normal[2]</t>
         </is>
       </c>
       <c r="B459" t="inlineStr" s="2">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="D459" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.normal[2]</t>
+          <t xml:space="preserve">GL-01.loss.standard.normal[2]</t>
         </is>
       </c>
       <c r="E459" t="inlineStr" s="2">
@@ -15084,14 +15084,14 @@
       </c>
       <c r="F459" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日はいい試合ができた</t>
+          <t xml:space="preserve">今日は相手が上だった。次は負けない</t>
         </is>
       </c>
     </row>
     <row r="460" ht="40" customHeight="1">
       <c r="A460" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.normal[1]</t>
         </is>
       </c>
       <c r="B460" t="inlineStr" s="2">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="D460" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.normal[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.normal[1]</t>
         </is>
       </c>
       <c r="E460" t="inlineStr" s="2">
@@ -15116,14 +15116,14 @@
       </c>
       <c r="F460" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日の練習はいい感じだ</t>
+          <t xml:space="preserve">よし、勝てた。この調子で頑張ろう</t>
         </is>
       </c>
     </row>
     <row r="461" ht="40" customHeight="1">
       <c r="A461" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.normal[2]</t>
         </is>
       </c>
       <c r="B461" t="inlineStr" s="2">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="D461" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.normal[2]</t>
+          <t xml:space="preserve">GL-01.win.standard.normal[2]</t>
         </is>
       </c>
       <c r="E461" t="inlineStr" s="2">
@@ -15148,14 +15148,14 @@
       </c>
       <c r="F461" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しスタミナつけないとな…</t>
+          <t xml:space="preserve">今日はいい試合ができた</t>
         </is>
       </c>
     </row>
     <row r="462" ht="40" customHeight="1">
       <c r="A462" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.normal[1]</t>
         </is>
       </c>
       <c r="B462" t="inlineStr" s="2">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="D462" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.normal[1]</t>
+          <t xml:space="preserve">GL-02.standard.normal[1]</t>
         </is>
       </c>
       <c r="E462" t="inlineStr" s="2">
@@ -15180,14 +15180,14 @@
       </c>
       <c r="F462" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…なんだか扱いが雑じゃないか…？</t>
+          <t xml:space="preserve">今日の練習はいい感じだ</t>
         </is>
       </c>
     </row>
     <row r="463" ht="40" customHeight="1">
       <c r="A463" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.normal[2]</t>
         </is>
       </c>
       <c r="B463" t="inlineStr" s="2">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="D463" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.normal[2]</t>
+          <t xml:space="preserve">GL-02.standard.normal[2]</t>
         </is>
       </c>
       <c r="E463" t="inlineStr" s="2">
@@ -15212,14 +15212,14 @@
       </c>
       <c r="F463" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと不安になってきた…大丈夫かな</t>
+          <t xml:space="preserve">もう少しスタミナつけないとな…</t>
         </is>
       </c>
     </row>
     <row r="464" ht="40" customHeight="1">
       <c r="A464" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.normal[1]</t>
         </is>
       </c>
       <c r="B464" t="inlineStr" s="2">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="D464" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.normal[1]</t>
         </is>
       </c>
       <c r="E464" t="inlineStr" s="2">
@@ -15244,14 +15244,14 @@
       </c>
       <c r="F464" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近いい感じだ。この団体で頑張ろうって思える</t>
+          <t xml:space="preserve">最近…なんだか扱いが雑じゃないか…？</t>
         </is>
       </c>
     </row>
     <row r="465" ht="40" customHeight="1">
       <c r="A465" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.normal[2]</t>
         </is>
       </c>
       <c r="B465" t="inlineStr" s="2">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="D465" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.normal[2]</t>
+          <t xml:space="preserve">GL-03.down.standard.normal[2]</t>
         </is>
       </c>
       <c r="E465" t="inlineStr" s="2">
@@ -15276,14 +15276,14 @@
       </c>
       <c r="F465" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんと見てくれてるんだな。嬉しいよ</t>
+          <t xml:space="preserve">ちょっと不安になってきた…大丈夫かな</t>
         </is>
       </c>
     </row>
     <row r="466" ht="40" customHeight="1">
       <c r="A466" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.normal[1]</t>
         </is>
       </c>
       <c r="B466" t="inlineStr" s="2">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="D466" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.normal[1]</t>
         </is>
       </c>
       <c r="E466" t="inlineStr" s="2">
@@ -15308,14 +15308,14 @@
       </c>
       <c r="F466" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると練習も楽しいんだよな</t>
+          <t xml:space="preserve">最近いい感じだ。この団体で頑張ろうって思える</t>
         </is>
       </c>
     </row>
     <row r="467" ht="40" customHeight="1">
       <c r="A467" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.normal[2]</t>
         </is>
       </c>
       <c r="B467" t="inlineStr" s="2">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="D467" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.normal[2]</t>
+          <t xml:space="preserve">GL-03.up.standard.normal[2]</t>
         </is>
       </c>
       <c r="E467" t="inlineStr" s="2">
@@ -15340,14 +15340,14 @@
       </c>
       <c r="F467" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近調子良さそうだな。嬉しいな</t>
+          <t xml:space="preserve">ちゃんと見てくれてるんだな。嬉しいよ</t>
         </is>
       </c>
     </row>
     <row r="468" ht="40" customHeight="1">
       <c r="A468" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.normal[1]</t>
         </is>
       </c>
       <c r="B468" t="inlineStr" s="2">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="D468" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.normal[1]</t>
+          <t xml:space="preserve">GL-04.standard.normal[1]</t>
         </is>
       </c>
       <c r="E468" t="inlineStr" s="2">
@@ -15372,14 +15372,14 @@
       </c>
       <c r="F468" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今何してるかな…気になる</t>
+          <t xml:space="preserve">一緒にいると練習も楽しいんだよな</t>
         </is>
       </c>
     </row>
     <row r="469" ht="40" customHeight="1">
       <c r="A469" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.normal[2]</t>
         </is>
       </c>
       <c r="B469" t="inlineStr" s="2">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="D469" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.normal[2]</t>
+          <t xml:space="preserve">GL-04.standard.normal[2]</t>
         </is>
       </c>
       <c r="E469" t="inlineStr" s="2">
@@ -15404,14 +15404,14 @@
       </c>
       <c r="F469" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったって聞くと…悔しいな</t>
+          <t xml:space="preserve">最近調子良さそうだな。嬉しいな</t>
         </is>
       </c>
     </row>
     <row r="470" ht="40" customHeight="1">
       <c r="A470" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.normal[1]</t>
         </is>
       </c>
       <c r="B470" t="inlineStr" s="2">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="D470" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.normal[1]</t>
+          <t xml:space="preserve">GL-05.standard.normal[1]</t>
         </is>
       </c>
       <c r="E470" t="inlineStr" s="2">
@@ -15436,14 +15436,14 @@
       </c>
       <c r="F470" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今週は出番なしか…リングが恋しい</t>
+          <t xml:space="preserve">今何してるかな…気になる</t>
         </is>
       </c>
     </row>
     <row r="471" ht="40" customHeight="1">
       <c r="A471" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.normal[2]</t>
         </is>
       </c>
       <c r="B471" t="inlineStr" s="2">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="D471" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.normal[2]</t>
+          <t xml:space="preserve">GL-05.standard.normal[2]</t>
         </is>
       </c>
       <c r="E471" t="inlineStr" s="2">
@@ -15468,14 +15468,14 @@
       </c>
       <c r="F471" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合に出たい。見てるだけはつらい</t>
+          <t xml:space="preserve">勝ったって聞くと…悔しいな</t>
         </is>
       </c>
     </row>
     <row r="472" ht="40" customHeight="1">
       <c r="A472" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.normal[1]</t>
         </is>
       </c>
       <c r="B472" t="inlineStr" s="2">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="D472" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.normal[1]</t>
+          <t xml:space="preserve">GL-06.standard.normal[1]</t>
         </is>
       </c>
       <c r="E472" t="inlineStr" s="2">
@@ -15500,14 +15500,14 @@
       </c>
       <c r="F472" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が重い…コンディションが上がらない</t>
+          <t xml:space="preserve">今週は出番なしか…リングが恋しい</t>
         </is>
       </c>
     </row>
     <row r="473" ht="40" customHeight="1">
       <c r="A473" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.normal[2]</t>
         </is>
       </c>
       <c r="B473" t="inlineStr" s="2">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="D473" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.normal[2]</t>
+          <t xml:space="preserve">GL-06.standard.normal[2]</t>
         </is>
       </c>
       <c r="E473" t="inlineStr" s="2">
@@ -15532,14 +15532,14 @@
       </c>
       <c r="F473" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子悪いな…少し休んだ方がいいかも</t>
+          <t xml:space="preserve">試合に出たい。見てるだけはつらい</t>
         </is>
       </c>
     </row>
     <row r="474" ht="40" customHeight="1">
       <c r="A474" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.normal[1]</t>
         </is>
       </c>
       <c r="B474" t="inlineStr" s="2">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="D474" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.normal[1]</t>
+          <t xml:space="preserve">GL-07.standard.normal[1]</t>
         </is>
       </c>
       <c r="E474" t="inlineStr" s="2">
@@ -15564,14 +15564,14 @@
       </c>
       <c r="F474" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また負けた…どうすればいいんだ</t>
+          <t xml:space="preserve">体が重い…コンディションが上がらない</t>
         </is>
       </c>
     </row>
     <row r="475" ht="40" customHeight="1">
       <c r="A475" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.normal[2]</t>
         </is>
       </c>
       <c r="B475" t="inlineStr" s="2">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="D475" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.normal[2]</t>
+          <t xml:space="preserve">GL-07.standard.normal[2]</t>
         </is>
       </c>
       <c r="E475" t="inlineStr" s="2">
@@ -15596,14 +15596,14 @@
       </c>
       <c r="F475" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗が止まらない…自信がなくなってきた</t>
+          <t xml:space="preserve">調子悪いな…少し休んだ方がいいかも</t>
         </is>
       </c>
     </row>
     <row r="476" ht="40" customHeight="1">
       <c r="A476" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.normal[1]</t>
         </is>
       </c>
       <c r="B476" t="inlineStr" s="2">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="D476" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.normal[1]</t>
+          <t xml:space="preserve">GL-08.standard.normal[1]</t>
         </is>
       </c>
       <c r="E476" t="inlineStr" s="2">
@@ -15628,14 +15628,14 @@
       </c>
       <c r="F476" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい流れが来てる。この調子を維持したい</t>
+          <t xml:space="preserve">また負けた…どうすればいいんだ</t>
         </is>
       </c>
     </row>
     <row r="477" ht="40" customHeight="1">
       <c r="A477" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.normal[2]</t>
         </is>
       </c>
       <c r="B477" t="inlineStr" s="2">
@@ -15650,7 +15650,7 @@
       </c>
       <c r="D477" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.normal[2]</t>
+          <t xml:space="preserve">GL-08.standard.normal[2]</t>
         </is>
       </c>
       <c r="E477" t="inlineStr" s="2">
@@ -15660,14 +15660,14 @@
       </c>
       <c r="F477" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝中…自信がついてきた</t>
+          <t xml:space="preserve">連敗が止まらない…自信がなくなってきた</t>
         </is>
       </c>
     </row>
     <row r="478" ht="40" customHeight="1">
       <c r="A478" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.normal[1]</t>
         </is>
       </c>
       <c r="B478" t="inlineStr" s="2">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="D478" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.normal[1]</t>
+          <t xml:space="preserve">GL-09.standard.normal[1]</t>
         </is>
       </c>
       <c r="E478" t="inlineStr" s="2">
@@ -15692,14 +15692,14 @@
       </c>
       <c r="F478" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早くリングに戻りたい…体が疼く</t>
+          <t xml:space="preserve">いい流れが来てる。この調子を維持したい</t>
         </is>
       </c>
     </row>
     <row r="479" ht="40" customHeight="1">
       <c r="A479" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.normal[2]</t>
         </is>
       </c>
       <c r="B479" t="inlineStr" s="2">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="D479" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.normal[2]</t>
+          <t xml:space="preserve">GL-09.standard.normal[2]</t>
         </is>
       </c>
       <c r="E479" t="inlineStr" s="2">
@@ -15724,14 +15724,14 @@
       </c>
       <c r="F479" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我…早く治してくれ…</t>
+          <t xml:space="preserve">連勝中…自信がついてきた</t>
         </is>
       </c>
     </row>
     <row r="480" ht="40" customHeight="1">
       <c r="A480" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.normal[1]</t>
         </is>
       </c>
       <c r="B480" t="inlineStr" s="2">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="D480" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.standard.normal[1]</t>
+          <t xml:space="preserve">GL-10.standard.normal[1]</t>
         </is>
       </c>
       <c r="E480" t="inlineStr" s="2">
@@ -15756,14 +15756,14 @@
       </c>
       <c r="F480" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子のこと？……特に何も。視界に入れてないだけ</t>
+          <t xml:space="preserve">早くリングに戻りたい…体が疼く</t>
         </is>
       </c>
     </row>
     <row r="481" ht="40" customHeight="1">
       <c r="A481" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.normal[2]</t>
         </is>
       </c>
       <c r="B481" t="inlineStr" s="2">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="D481" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.standard.normal[2]</t>
+          <t xml:space="preserve">GL-10.standard.normal[2]</t>
         </is>
       </c>
       <c r="E481" t="inlineStr" s="2">
@@ -15788,14 +15788,14 @@
       </c>
       <c r="F481" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ場にいても、話すことは何もないかな</t>
+          <t xml:space="preserve">怪我…早く治さないと…</t>
         </is>
       </c>
     </row>
     <row r="482" ht="40" customHeight="1">
       <c r="A482" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.normal[1]</t>
         </is>
       </c>
       <c r="B482" t="inlineStr" s="2">
@@ -15805,12 +15805,12 @@
       </c>
       <c r="C482" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D482" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">GL-11.standard.normal[1]</t>
         </is>
       </c>
       <c r="E482" t="inlineStr" s="2">
@@ -15820,14 +15820,14 @@
       </c>
       <c r="F482" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調は終わったけど…あの期間は無駄じゃなかった</t>
+          <t xml:space="preserve">あの子のこと？……特に何も。視界に入れてないだけ</t>
         </is>
       </c>
     </row>
     <row r="483" ht="40" customHeight="1">
       <c r="A483" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.normal[2]</t>
         </is>
       </c>
       <c r="B483" t="inlineStr" s="2">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="C483" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D483" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">GL-11.standard.normal[2]</t>
         </is>
       </c>
       <c r="E483" t="inlineStr" s="2">
@@ -15852,14 +15852,14 @@
       </c>
       <c r="F483" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が落ち着いてきた。でも前より強くなってる気がする</t>
+          <t xml:space="preserve">同じ場にいても、話すことは何もないかな</t>
         </is>
       </c>
     </row>
     <row r="484" ht="40" customHeight="1">
       <c r="A484" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B484" t="inlineStr" s="2">
@@ -15869,29 +15869,29 @@
       </c>
       <c r="C484" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D484" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E484" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F484" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちこち痛むけど、ここまで残った。最後まで、リングは渡さない</t>
+          <t xml:space="preserve">絶好調は終わったけど…あの期間は無駄じゃなかった</t>
         </is>
       </c>
     </row>
     <row r="485" ht="40" customHeight="1">
       <c r="A485" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B485" t="inlineStr" s="2">
@@ -15901,29 +15901,29 @@
       </c>
       <c r="C485" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D485" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E485" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F485" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重い。でも、あと一つ。繋いできたものを、無駄にはしない</t>
+          <t xml:space="preserve">体が落ち着いてきた。でも前より強くなってる気がする</t>
         </is>
       </c>
     </row>
     <row r="486" ht="40" customHeight="1">
       <c r="A486" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.normal[1]</t>
         </is>
       </c>
       <c r="B486" t="inlineStr" s="2">
@@ -15938,7 +15938,7 @@
       </c>
       <c r="D486" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.normal[1]</t>
+          <t xml:space="preserve">preFinal.standard.normal[1]</t>
         </is>
       </c>
       <c r="E486" t="inlineStr" s="2">
@@ -15948,14 +15948,14 @@
       </c>
       <c r="F486" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どんな相手が来ても、やることは一つ。真っ向から受けて、次に繋ぐ</t>
+          <t xml:space="preserve">あちこち痛むけど、ここまで残った。最後まで、リングは渡さない</t>
         </is>
       </c>
     </row>
     <row r="487" ht="40" customHeight="1">
       <c r="A487" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.normal[2]</t>
         </is>
       </c>
       <c r="B487" t="inlineStr" s="2">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="D487" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.normal[2]</t>
+          <t xml:space="preserve">preFinal.standard.normal[2]</t>
         </is>
       </c>
       <c r="E487" t="inlineStr" s="2">
@@ -15980,14 +15980,14 @@
       </c>
       <c r="F487" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリングは譲らない。目の前の一人に、全部ぶつけるだけ</t>
+          <t xml:space="preserve">身体は重い。でも、あと一つ。繋いできたものを、無駄にはしない</t>
         </is>
       </c>
     </row>
     <row r="488" ht="40" customHeight="1">
       <c r="A488" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.normal[1]</t>
         </is>
       </c>
       <c r="B488" t="inlineStr" s="2">
@@ -16002,7 +16002,7 @@
       </c>
       <c r="D488" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.normal[1]</t>
+          <t xml:space="preserve">preMatch.standard.normal[1]</t>
         </is>
       </c>
       <c r="E488" t="inlineStr" s="2">
@@ -16012,14 +16012,14 @@
       </c>
       <c r="F488" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落とした。…息が上がってる。でも、リングは渡さない。次、来い</t>
+          <t xml:space="preserve">どんな相手が来ても、やることは一つ。真っ向から受けて、次に繋ぐ</t>
         </is>
       </c>
     </row>
     <row r="489" ht="40" customHeight="1">
       <c r="A489" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.normal[2]</t>
         </is>
       </c>
       <c r="B489" t="inlineStr" s="2">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="D489" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.normal[2]</t>
+          <t xml:space="preserve">preMatch.standard.normal[2]</t>
         </is>
       </c>
       <c r="E489" t="inlineStr" s="2">
@@ -16044,14 +16044,14 @@
       </c>
       <c r="F489" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってる。次の挑戦者、早く出てきて。ここは動かないから</t>
+          <t xml:space="preserve">このリングは譲らない。目の前の一人に、全部ぶつけるだけ</t>
         </is>
       </c>
     </row>
     <row r="490" ht="40" customHeight="1">
       <c r="A490" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.normal[1]</t>
         </is>
       </c>
       <c r="B490" t="inlineStr" s="2">
@@ -16061,12 +16061,12 @@
       </c>
       <c r="C490" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D490" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[1]</t>
+          <t xml:space="preserve">survivor.standard.normal[1]</t>
         </is>
       </c>
       <c r="E490" t="inlineStr" s="2">
@@ -16076,14 +16076,14 @@
       </c>
       <c r="F490" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私一人の勝利じゃない。先鋒から大将まで、三人でつないだ勝利です</t>
+          <t xml:space="preserve">一人、落とした。…息が上がってる。でも、リングは渡さない。次、来い</t>
         </is>
       </c>
     </row>
     <row r="491" ht="40" customHeight="1">
       <c r="A491" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.normal[2]</t>
         </is>
       </c>
       <c r="B491" t="inlineStr" s="2">
@@ -16093,12 +16093,12 @@
       </c>
       <c r="C491" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D491" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[2]</t>
+          <t xml:space="preserve">survivor.standard.normal[2]</t>
         </is>
       </c>
       <c r="E491" t="inlineStr" s="2">
@@ -16108,14 +16108,14 @@
       </c>
       <c r="F491" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人の力を合わせて、ここまで来ました。一人じゃ絶対にたどり着けなかった</t>
+          <t xml:space="preserve">まだ立ってる。次の挑戦者、早く出てきて。ここは動かないから</t>
         </is>
       </c>
     </row>
     <row r="492" ht="40" customHeight="1">
       <c r="A492" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[1]</t>
         </is>
       </c>
       <c r="B492" t="inlineStr" s="2">
@@ -16130,7 +16130,7 @@
       </c>
       <c r="D492" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[3]</t>
+          <t xml:space="preserve">champion.standard.normal[1]</t>
         </is>
       </c>
       <c r="E492" t="inlineStr" s="2">
@@ -16140,14 +16140,14 @@
       </c>
       <c r="F492" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれたから、私はこのリングに立てている。感謝しかない</t>
+          <t xml:space="preserve">私一人の勝利じゃない。先鋒から大将まで、三人でつないだ勝利です</t>
         </is>
       </c>
     </row>
     <row r="493" ht="40" customHeight="1">
       <c r="A493" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[2]</t>
         </is>
       </c>
       <c r="B493" t="inlineStr" s="2">
@@ -16162,7 +16162,7 @@
       </c>
       <c r="D493" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.normal[1]</t>
+          <t xml:space="preserve">champion.standard.normal[2]</t>
         </is>
       </c>
       <c r="E493" t="inlineStr" s="2">
@@ -16172,14 +16172,14 @@
       </c>
       <c r="F493" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPでも、団体が負けた事実は消えない。次は、最後の一人まで残ります</t>
+          <t xml:space="preserve">三人の力を合わせて、ここまで来ました。一人じゃ絶対にたどり着けなかった</t>
         </is>
       </c>
     </row>
     <row r="494" ht="40" customHeight="1">
       <c r="A494" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[3]</t>
         </is>
       </c>
       <c r="B494" t="inlineStr" s="2">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="D494" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.normal[2]</t>
+          <t xml:space="preserve">champion.standard.normal[3]</t>
         </is>
       </c>
       <c r="E494" t="inlineStr" s="2">
@@ -16204,14 +16204,14 @@
       </c>
       <c r="F494" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞は嬉しい。でも、それだけじゃ足りない。次は団体ごと勝つ</t>
+          <t xml:space="preserve">仲間が繋いでくれたから、私はこのリングに立てている。感謝しかない</t>
         </is>
       </c>
     </row>
     <row r="495" ht="40" customHeight="1">
       <c r="A495" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[1]</t>
         </is>
       </c>
       <c r="B495" t="inlineStr" s="2">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="D495" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.normal[3]</t>
+          <t xml:space="preserve">defiant.standard.normal[1]</t>
         </is>
       </c>
       <c r="E495" t="inlineStr" s="2">
@@ -16236,14 +16236,14 @@
       </c>
       <c r="F495" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の評価で満足するわけにはいかない。次こそ、みんなで頂点に立つ</t>
+          <t xml:space="preserve">MVPでも、団体が負けた事実は消えない。次は、最後の一人まで残ります</t>
         </is>
       </c>
     </row>
     <row r="496" ht="40" customHeight="1">
       <c r="A496" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[2]</t>
         </is>
       </c>
       <c r="B496" t="inlineStr" s="2">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="D496" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.normal[1]</t>
+          <t xml:space="preserve">defiant.standard.normal[2]</t>
         </is>
       </c>
       <c r="E496" t="inlineStr" s="2">
@@ -16268,14 +16268,14 @@
       </c>
       <c r="F496" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">脚がもう動かない。でも、最後までリングを譲らなかった。それだけは誇っていいと思う</t>
+          <t xml:space="preserve">この賞は嬉しい。でも、それだけじゃ足りない。次は団体ごと勝つ</t>
         </is>
       </c>
     </row>
     <row r="497" ht="40" customHeight="1">
       <c r="A497" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[3]</t>
         </is>
       </c>
       <c r="B497" t="inlineStr" s="2">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="D497" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.normal[2]</t>
+          <t xml:space="preserve">defiant.standard.normal[3]</t>
         </is>
       </c>
       <c r="E497" t="inlineStr" s="2">
@@ -16300,14 +16300,14 @@
       </c>
       <c r="F497" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人倒したか、もう数えてない。ただ、一度も膝をつかなかった。それだけ覚えてる</t>
+          <t xml:space="preserve">個人の評価で満足するわけにはいかない。次こそ、みんなで頂点に立つ</t>
         </is>
       </c>
     </row>
     <row r="498" ht="40" customHeight="1">
       <c r="A498" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[1]</t>
         </is>
       </c>
       <c r="B498" t="inlineStr" s="2">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="D498" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.normal[3]</t>
+          <t xml:space="preserve">gauntlet.standard.normal[1]</t>
         </is>
       </c>
       <c r="E498" t="inlineStr" s="2">
@@ -16332,14 +16332,14 @@
       </c>
       <c r="F498" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼろぼろだけど、立ってる。それが今日の私の答え</t>
+          <t xml:space="preserve">脚がもう動かない。でも、最後までリングを譲らなかった。それだけは誇っていいと思う</t>
         </is>
       </c>
     </row>
     <row r="499" ht="40" customHeight="1">
       <c r="A499" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[2]</t>
         </is>
       </c>
       <c r="B499" t="inlineStr" s="2">
@@ -16349,12 +16349,12 @@
       </c>
       <c r="C499" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D499" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[1]</t>
+          <t xml:space="preserve">gauntlet.standard.normal[2]</t>
         </is>
       </c>
       <c r="E499" t="inlineStr" s="2">
@@ -16364,14 +16364,14 @@
       </c>
       <c r="F499" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この優勝を、次のステップにする</t>
+          <t xml:space="preserve">何人倒したか、もう数えてない。ただ、一度も膝をつかなかった。それだけ覚えてる</t>
         </is>
       </c>
     </row>
     <row r="500" ht="40" customHeight="1">
       <c r="A500" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[3]</t>
         </is>
       </c>
       <c r="B500" t="inlineStr" s="2">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="C500" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D500" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[2]</t>
+          <t xml:space="preserve">gauntlet.standard.normal[3]</t>
         </is>
       </c>
       <c r="E500" t="inlineStr" s="2">
@@ -16396,14 +16396,14 @@
       </c>
       <c r="F500" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝。嬉しい。でも、これで終わりじゃない</t>
+          <t xml:space="preserve">ぼろぼろだけど、立ってる。それが今日の私の答え</t>
         </is>
       </c>
     </row>
     <row r="501" ht="40" customHeight="1">
       <c r="A501" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.normal[1]</t>
         </is>
       </c>
       <c r="B501" t="inlineStr" s="2">
@@ -16418,7 +16418,7 @@
       </c>
       <c r="D501" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.normal[1]</t>
+          <t xml:space="preserve">champion.standard.normal[1]</t>
         </is>
       </c>
       <c r="E501" t="inlineStr" s="2">
@@ -16428,14 +16428,14 @@
       </c>
       <c r="F501" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…。でも、次に繋げる</t>
+          <t xml:space="preserve">この優勝を、次のステップにする</t>
         </is>
       </c>
     </row>
     <row r="502" ht="40" customHeight="1">
       <c r="A502" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.normal[2]</t>
         </is>
       </c>
       <c r="B502" t="inlineStr" s="2">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="D502" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.normal[2]</t>
+          <t xml:space="preserve">champion.standard.normal[2]</t>
         </is>
       </c>
       <c r="E502" t="inlineStr" s="2">
@@ -16460,14 +16460,14 @@
       </c>
       <c r="F502" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力不足を痛感した。もっと強くならないと</t>
+          <t xml:space="preserve">優勝。嬉しい。でも、これで終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="503" ht="40" customHeight="1">
       <c r="A503" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.normal[1]</t>
         </is>
       </c>
       <c r="B503" t="inlineStr" s="2">
@@ -16482,7 +16482,7 @@
       </c>
       <c r="D503" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.normal[1]</t>
+          <t xml:space="preserve">postLose.standard.normal[1]</t>
         </is>
       </c>
       <c r="E503" t="inlineStr" s="2">
@@ -16492,14 +16492,14 @@
       </c>
       <c r="F503" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一つクリア。次に集中する</t>
+          <t xml:space="preserve">悔しい…。でも、次に繋げる</t>
         </is>
       </c>
     </row>
     <row r="504" ht="40" customHeight="1">
       <c r="A504" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.normal[2]</t>
         </is>
       </c>
       <c r="B504" t="inlineStr" s="2">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="D504" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.normal[2]</t>
+          <t xml:space="preserve">postLose.standard.normal[2]</t>
         </is>
       </c>
       <c r="E504" t="inlineStr" s="2">
@@ -16524,14 +16524,14 @@
       </c>
       <c r="F504" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った。でも気を抜かない</t>
+          <t xml:space="preserve">力不足を痛感した。もっと強くならないと</t>
         </is>
       </c>
     </row>
     <row r="505" ht="40" customHeight="1">
       <c r="A505" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="B505" t="inlineStr" s="2">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="D505" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="E505" t="inlineStr" s="2">
@@ -16556,14 +16556,14 @@
       </c>
       <c r="F505" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験になった。もっと強くなりたい</t>
+          <t xml:space="preserve">一つクリア。次に集中する</t>
         </is>
       </c>
     </row>
     <row r="506" ht="40" customHeight="1">
       <c r="A506" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="B506" t="inlineStr" s="2">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="D506" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="E506" t="inlineStr" s="2">
@@ -16588,14 +16588,14 @@
       </c>
       <c r="F506" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大会を通して、自分の成長を感じられた</t>
+          <t xml:space="preserve">勝った。でも気を抜かない</t>
         </is>
       </c>
     </row>
     <row r="507" ht="40" customHeight="1">
       <c r="A507" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="B507" t="inlineStr" s="2">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="D507" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.normal[1]</t>
+          <t xml:space="preserve">postWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="E507" t="inlineStr" s="2">
@@ -16620,14 +16620,14 @@
       </c>
       <c r="F507" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ。勝てば優勝。それだけ考える</t>
+          <t xml:space="preserve">いい経験になった。もっと強くなりたい</t>
         </is>
       </c>
     </row>
     <row r="508" ht="40" customHeight="1">
       <c r="A508" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="B508" t="inlineStr" s="2">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="D508" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.normal[2]</t>
+          <t xml:space="preserve">postWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="E508" t="inlineStr" s="2">
@@ -16652,14 +16652,14 @@
       </c>
       <c r="F508" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝。全てを懸ける</t>
+          <t xml:space="preserve">大会を通して、自分の成長を感じられた</t>
         </is>
       </c>
     </row>
     <row r="509" ht="40" customHeight="1">
       <c r="A509" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.normal[1]</t>
         </is>
       </c>
       <c r="B509" t="inlineStr" s="2">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="D509" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.normal[1]</t>
+          <t xml:space="preserve">preFinal.standard.normal[1]</t>
         </is>
       </c>
       <c r="E509" t="inlineStr" s="2">
@@ -16684,14 +16684,14 @@
       </c>
       <c r="F509" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどうとかじゃない。自分の試合をする</t>
+          <t xml:space="preserve">あと一つ。勝てば優勝。それだけ考える</t>
         </is>
       </c>
     </row>
     <row r="510" ht="40" customHeight="1">
       <c r="A510" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.normal[2]</t>
         </is>
       </c>
       <c r="B510" t="inlineStr" s="2">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="D510" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.normal[2]</t>
+          <t xml:space="preserve">preFinal.standard.normal[2]</t>
         </is>
       </c>
       <c r="E510" t="inlineStr" s="2">
@@ -16716,14 +16716,14 @@
       </c>
       <c r="F510" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">集中。一つずつ勝っていく</t>
+          <t xml:space="preserve">決勝。全てを懸ける</t>
         </is>
       </c>
     </row>
     <row r="511" ht="40" customHeight="1">
       <c r="A511" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.normal[1]</t>
         </is>
       </c>
       <c r="B511" t="inlineStr" s="2">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="D511" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.normal[1]</t>
+          <t xml:space="preserve">preMatch.standard.normal[1]</t>
         </is>
       </c>
       <c r="E511" t="inlineStr" s="2">
@@ -16748,14 +16748,14 @@
       </c>
       <c r="F511" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ばれたからには、全力で戦う</t>
+          <t xml:space="preserve">相手がどうとかじゃない。自分の試合をする</t>
         </is>
       </c>
     </row>
     <row r="512" ht="40" customHeight="1">
       <c r="A512" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.normal[2]</t>
         </is>
       </c>
       <c r="B512" t="inlineStr" s="2">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="D512" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.normal[2]</t>
+          <t xml:space="preserve">preMatch.standard.normal[2]</t>
         </is>
       </c>
       <c r="E512" t="inlineStr" s="2">
@@ -16780,14 +16780,14 @@
       </c>
       <c r="F512" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この舞台に立てることを誇りに思う</t>
+          <t xml:space="preserve">集中。一つずつ勝っていく</t>
         </is>
       </c>
     </row>
     <row r="513" ht="40" customHeight="1">
       <c r="A513" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.normal[1]</t>
         </is>
       </c>
       <c r="B513" t="inlineStr" s="2">
@@ -16797,12 +16797,12 @@
       </c>
       <c r="C513" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D513" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">summon.standard.normal[1]</t>
         </is>
       </c>
       <c r="E513" t="inlineStr" s="2">
@@ -16812,14 +16812,14 @@
       </c>
       <c r="F513" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪いけど、今日は負けるわけにはいかないの</t>
+          <t xml:space="preserve">選ばれたからには、全力で戦う</t>
         </is>
       </c>
     </row>
     <row r="514" ht="40" customHeight="1">
       <c r="A514" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.normal[2]</t>
         </is>
       </c>
       <c r="B514" t="inlineStr" s="2">
@@ -16829,12 +16829,12 @@
       </c>
       <c r="C514" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D514" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">summon.standard.normal[2]</t>
         </is>
       </c>
       <c r="E514" t="inlineStr" s="2">
@@ -16844,14 +16844,14 @@
       </c>
       <c r="F514" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台、最高の気分ね</t>
+          <t xml:space="preserve">この舞台に立てることを誇りに思う</t>
         </is>
       </c>
     </row>
     <row r="515" ht="40" customHeight="1">
       <c r="A515" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B515" t="inlineStr" s="2">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="D515" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E515" t="inlineStr" s="2">
@@ -16876,14 +16876,14 @@
       </c>
       <c r="F515" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正々堂々、最高の試合にしましょう</t>
+          <t xml:space="preserve">悪いけど、今日は負けるわけにはいかないの</t>
         </is>
       </c>
     </row>
     <row r="516" ht="40" customHeight="1">
       <c r="A516" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B516" t="inlineStr" s="2">
@@ -16893,12 +16893,12 @@
       </c>
       <c r="C516" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D516" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E516" t="inlineStr" s="2">
@@ -16908,14 +16908,14 @@
       </c>
       <c r="F516" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やった。本当に、やったんだ……！</t>
+          <t xml:space="preserve">この大舞台、最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="517" ht="40" customHeight="1">
       <c r="A517" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B517" t="inlineStr" s="2">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="C517" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D517" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E517" t="inlineStr" s="2">
@@ -16940,14 +16940,14 @@
       </c>
       <c r="F517" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのおかげです。この舞台で勝てて、本当に嬉しい</t>
+          <t xml:space="preserve">正々堂々、最高の試合にしましょう</t>
         </is>
       </c>
     </row>
     <row r="518" ht="40" customHeight="1">
       <c r="A518" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B518" t="inlineStr" s="2">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="D518" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E518" t="inlineStr" s="2">
@@ -16972,14 +16972,14 @@
       </c>
       <c r="F518" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じてくれた人たちに、やっと恩返しができた気がする</t>
+          <t xml:space="preserve">……やった。本当に、やったんだ……！</t>
         </is>
       </c>
     </row>
     <row r="519" ht="40" customHeight="1">
       <c r="A519" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B519" t="inlineStr" s="2">
@@ -16989,12 +16989,12 @@
       </c>
       <c r="C519" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D519" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E519" t="inlineStr" s="2">
@@ -17004,14 +17004,14 @@
       </c>
       <c r="F519" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたたちの実力、確かめさせてもらうよ</t>
+          <t xml:space="preserve">みんなのおかげです。この舞台で勝てて、本当に嬉しい</t>
         </is>
       </c>
     </row>
     <row r="520" ht="40" customHeight="1">
       <c r="A520" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B520" t="inlineStr" s="2">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="C520" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D520" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E520" t="inlineStr" s="2">
@@ -17036,14 +17036,14 @@
       </c>
       <c r="F520" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こっちは本気だよ。受けて立つ気はあるの？</t>
+          <t xml:space="preserve">信じてくれた人たちに、やっと恩返しができた気がする</t>
         </is>
       </c>
     </row>
     <row r="521" ht="40" customHeight="1">
       <c r="A521" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.normal[1]</t>
         </is>
       </c>
       <c r="B521" t="inlineStr" s="2">
@@ -17053,7 +17053,7 @@
       </c>
       <c r="C521" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D521" t="inlineStr" s="12">
@@ -17068,14 +17068,14 @@
       </c>
       <c r="F521" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっぱりな。逃げると思ってたよ</t>
+          <t xml:space="preserve">あんたたちの実力、確かめさせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="522" ht="40" customHeight="1">
       <c r="A522" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.normal[2]</t>
         </is>
       </c>
       <c r="B522" t="inlineStr" s="2">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="C522" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D522" t="inlineStr" s="12">
@@ -17100,14 +17100,14 @@
       </c>
       <c r="F522" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げ足だけは一流だね</t>
+          <t xml:space="preserve">こっちは本気だよ。受けて立つ気はある？</t>
         </is>
       </c>
     </row>
     <row r="523" ht="40" customHeight="1">
       <c r="A523" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.normal[1]</t>
         </is>
       </c>
       <c r="B523" t="inlineStr" s="2">
@@ -17117,12 +17117,12 @@
       </c>
       <c r="C523" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D523" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E523" t="inlineStr" s="2">
@@ -17132,14 +17132,14 @@
       </c>
       <c r="F523" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど…結果は結果。次は絶対に負けない</t>
+          <t xml:space="preserve">やっぱりね。逃げるだろうなって思ってた</t>
         </is>
       </c>
     </row>
     <row r="524" ht="40" customHeight="1">
       <c r="A524" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.normal[2]</t>
         </is>
       </c>
       <c r="B524" t="inlineStr" s="2">
@@ -17149,12 +17149,12 @@
       </c>
       <c r="C524" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D524" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E524" t="inlineStr" s="2">
@@ -17164,14 +17164,14 @@
       </c>
       <c r="F524" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借りは…必ず返す</t>
+          <t xml:space="preserve">…逃げ足だけは速いんだね</t>
         </is>
       </c>
     </row>
     <row r="525" ht="40" customHeight="1">
       <c r="A525" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.normal[1]</t>
         </is>
       </c>
       <c r="B525" t="inlineStr" s="2">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="D525" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.normal[1]</t>
+          <t xml:space="preserve">result_lose.standard.normal[1]</t>
         </is>
       </c>
       <c r="E525" t="inlineStr" s="2">
@@ -17196,14 +17196,14 @@
       </c>
       <c r="F525" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた。うちの団体の強さを見せられたと思う</t>
+          <t xml:space="preserve">悔しいけど…結果は結果。次は絶対に負けない</t>
         </is>
       </c>
     </row>
     <row r="526" ht="40" customHeight="1">
       <c r="A526" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.normal[2]</t>
         </is>
       </c>
       <c r="B526" t="inlineStr" s="2">
@@ -17218,7 +17218,7 @@
       </c>
       <c r="D526" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.normal[2]</t>
+          <t xml:space="preserve">result_lose.standard.normal[2]</t>
         </is>
       </c>
       <c r="E526" t="inlineStr" s="2">
@@ -17228,14 +17228,14 @@
       </c>
       <c r="F526" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦だった。この経験を次に活かそう</t>
+          <t xml:space="preserve">この借りは…必ず返す</t>
         </is>
       </c>
     </row>
     <row r="527" ht="40" customHeight="1">
       <c r="A527" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.normal[1]</t>
         </is>
       </c>
       <c r="B527" t="inlineStr" s="2">
@@ -17245,12 +17245,12 @@
       </c>
       <c r="C527" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D527" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">result_win.standard.normal[1]</t>
         </is>
       </c>
       <c r="E527" t="inlineStr" s="2">
@@ -17260,14 +17260,14 @@
       </c>
       <c r="F527" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの団体の強さ、見せられたと思います</t>
+          <t xml:space="preserve">勝てた。うちの団体の強さを見せられたと思う</t>
         </is>
       </c>
     </row>
     <row r="528" ht="40" customHeight="1">
       <c r="A528" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.normal[2]</t>
         </is>
       </c>
       <c r="B528" t="inlineStr" s="2">
@@ -17277,12 +17277,12 @@
       </c>
       <c r="C528" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D528" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">result_win.standard.normal[2]</t>
         </is>
       </c>
       <c r="E528" t="inlineStr" s="2">
@@ -17292,14 +17292,14 @@
       </c>
       <c r="F528" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てて良かった。団体の看板は守れた</t>
+          <t xml:space="preserve">いい対抗戦だった。この経験を次に活かそう</t>
         </is>
       </c>
     </row>
     <row r="529" ht="40" customHeight="1">
       <c r="A529" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B529" t="inlineStr" s="2">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="D529" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E529" t="inlineStr" s="2">
@@ -17324,14 +17324,14 @@
       </c>
       <c r="F529" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一つ勝てた。みんなの期待に応えられたかな</t>
+          <t xml:space="preserve">うちの団体の強さ、見せられたと思います</t>
         </is>
       </c>
     </row>
     <row r="530" ht="40" customHeight="1">
       <c r="A530" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B530" t="inlineStr" s="2">
@@ -17341,29 +17341,29 @@
       </c>
       <c r="C530" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D530" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E530" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F530" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体で戦えて、本当に良かった</t>
+          <t xml:space="preserve">勝てて良かった。団体の看板は守れた</t>
         </is>
       </c>
     </row>
     <row r="531" ht="40" customHeight="1">
       <c r="A531" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B531" t="inlineStr" s="2">
@@ -17373,29 +17373,29 @@
       </c>
       <c r="C531" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D531" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E531" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F531" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">入団した時は、まさかここまで来れるなんて思わなかった</t>
+          <t xml:space="preserve">一つ勝てた。みんなの期待に応えられたかな</t>
         </is>
       </c>
     </row>
     <row r="532" ht="40" customHeight="1">
       <c r="A532" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[3]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[1]</t>
         </is>
       </c>
       <c r="B532" t="inlineStr" s="2">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="D532" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.normal[3]</t>
+          <t xml:space="preserve">fighter.standard.normal[1]</t>
         </is>
       </c>
       <c r="E532" t="inlineStr" s="2">
@@ -17420,14 +17420,14 @@
       </c>
       <c r="F532" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の仲間と、最高の舞台。感謝しかないよ</t>
+          <t xml:space="preserve">この団体で戦えて、本当に良かった</t>
         </is>
       </c>
     </row>
     <row r="533" ht="40" customHeight="1">
       <c r="A533" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[2]</t>
         </is>
       </c>
       <c r="B533" t="inlineStr" s="2">
@@ -17437,29 +17437,29 @@
       </c>
       <c r="C533" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D533" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">fighter.standard.normal[2]</t>
         </is>
       </c>
       <c r="E533" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F533" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">所属が決まるって、やっぱり落ち着くね</t>
+          <t xml:space="preserve">入団した時は、まさかここまで来れるなんて思わなかった</t>
         </is>
       </c>
     </row>
     <row r="534" ht="40" customHeight="1">
       <c r="A534" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[3]</t>
         </is>
       </c>
       <c r="B534" t="inlineStr" s="2">
@@ -17469,29 +17469,29 @@
       </c>
       <c r="C534" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D534" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">fighter.standard.normal[3]</t>
         </is>
       </c>
       <c r="E534" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F534" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また声がかかって嬉しいよ。今度は長くいたいね</t>
+          <t xml:space="preserve">最高の仲間と、最高の舞台。感謝しかないよ</t>
         </is>
       </c>
     </row>
     <row r="535" ht="40" customHeight="1">
       <c r="A535" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B535" t="inlineStr" s="2">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="D535" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E535" t="inlineStr" s="2">
@@ -17516,14 +17516,14 @@
       </c>
       <c r="F535" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーも気楽だったけど、やっぱりリングが一番だね</t>
+          <t xml:space="preserve">所属が決まるって、やっぱり落ち着くね</t>
         </is>
       </c>
     </row>
     <row r="536" ht="40" customHeight="1">
       <c r="A536" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B536" t="inlineStr" s="2">
@@ -17533,12 +17533,12 @@
       </c>
       <c r="C536" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D536" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E536" t="inlineStr" s="2">
@@ -17548,14 +17548,14 @@
       </c>
       <c r="F536" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくれた目を信じて、頑張ってみるね</t>
+          <t xml:space="preserve">また声がかかって嬉しいよ。今度は長くいたいね</t>
         </is>
       </c>
     </row>
     <row r="537" ht="40" customHeight="1">
       <c r="A537" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B537" t="inlineStr" s="2">
@@ -17565,12 +17565,12 @@
       </c>
       <c r="C537" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D537" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E537" t="inlineStr" s="2">
@@ -17580,44 +17580,108 @@
       </c>
       <c r="F537" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさか自分に声がかかるとはね。よろしく</t>
+          <t xml:space="preserve">フリーも気楽だったけど、やっぱりリングが一番だね</t>
         </is>
       </c>
     </row>
     <row r="538" ht="40" customHeight="1">
       <c r="A538" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてくれた目を信じて、頑張ってみるね</t>
+        </is>
+      </c>
+    </row>
+    <row r="539" ht="40" customHeight="1">
+      <c r="A539" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まさか自分に声がかかるとはね。よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="40" customHeight="1">
+      <c r="A540" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.normal[3]</t>
         </is>
       </c>
-      <c r="B538" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C538" t="inlineStr" s="2">
+      <c r="B540" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr" s="12">
+      <c r="D540" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
-      <c r="E538" t="inlineStr" s="2">
+      <c r="E540" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F538" t="inlineStr" s="3">
+      <c r="F540" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">期待されてるうちに、いいとこ見せないとね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H538"/>
+  <autoFilter ref="A1:H540"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
@@ -372,7 +372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H540"/>
+  <dimension ref="A1:H545"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -15155,7 +15155,7 @@
     <row r="462" ht="40" customHeight="1">
       <c r="A462" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.normal[1]</t>
         </is>
       </c>
       <c r="B462" t="inlineStr" s="2">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="D462" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.normal[1]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.normal[1]</t>
         </is>
       </c>
       <c r="E462" t="inlineStr" s="2">
@@ -15180,14 +15180,14 @@
       </c>
       <c r="F462" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日の練習はいい感じだ</t>
+          <t xml:space="preserve">あいつのことを考えると、練習に身が入らない…</t>
         </is>
       </c>
     </row>
     <row r="463" ht="40" customHeight="1">
       <c r="A463" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.normal[2]</t>
         </is>
       </c>
       <c r="B463" t="inlineStr" s="2">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="D463" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.normal[2]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.normal[2]</t>
         </is>
       </c>
       <c r="E463" t="inlineStr" s="2">
@@ -15212,14 +15212,14 @@
       </c>
       <c r="F463" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう少しスタミナつけないとな…</t>
+          <t xml:space="preserve">次に当たったとき…絶対に見てろよ</t>
         </is>
       </c>
     </row>
     <row r="464" ht="40" customHeight="1">
       <c r="A464" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.normal[3]</t>
         </is>
       </c>
       <c r="B464" t="inlineStr" s="2">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="D464" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.normal[1]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.normal[3]</t>
         </is>
       </c>
       <c r="E464" t="inlineStr" s="2">
@@ -15244,14 +15244,14 @@
       </c>
       <c r="F464" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近…なんだか扱いが雑じゃないか…？</t>
+          <t xml:space="preserve">なんであいつが同じ場所にいるんだ。意味わからん</t>
         </is>
       </c>
     </row>
     <row r="465" ht="40" customHeight="1">
       <c r="A465" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.normal[4]</t>
         </is>
       </c>
       <c r="B465" t="inlineStr" s="2">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="D465" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.normal[2]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.normal[4]</t>
         </is>
       </c>
       <c r="E465" t="inlineStr" s="2">
@@ -15276,14 +15276,14 @@
       </c>
       <c r="F465" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちょっと不安になってきた…大丈夫かな</t>
+          <t xml:space="preserve">…練習中に思い出すな。腹が立って仕方ない</t>
         </is>
       </c>
     </row>
     <row r="466" ht="40" customHeight="1">
       <c r="A466" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.normal[5]</t>
         </is>
       </c>
       <c r="B466" t="inlineStr" s="2">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="D466" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.normal[1]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.normal[5]</t>
         </is>
       </c>
       <c r="E466" t="inlineStr" s="2">
@@ -15308,14 +15308,14 @@
       </c>
       <c r="F466" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近いい感じだ。この団体で頑張ろうって思える</t>
+          <t xml:space="preserve">こっちがどれだけ頑張っても、あいつのことが頭から離れない</t>
         </is>
       </c>
     </row>
     <row r="467" ht="40" customHeight="1">
       <c r="A467" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.normal[1]</t>
         </is>
       </c>
       <c r="B467" t="inlineStr" s="2">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="D467" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.normal[2]</t>
+          <t xml:space="preserve">GL-02.standard.normal[1]</t>
         </is>
       </c>
       <c r="E467" t="inlineStr" s="2">
@@ -15340,14 +15340,14 @@
       </c>
       <c r="F467" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちゃんと見てくれてるんだな。嬉しいよ</t>
+          <t xml:space="preserve">今日の練習はいい感じだ</t>
         </is>
       </c>
     </row>
     <row r="468" ht="40" customHeight="1">
       <c r="A468" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.normal[2]</t>
         </is>
       </c>
       <c r="B468" t="inlineStr" s="2">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="D468" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.normal[1]</t>
+          <t xml:space="preserve">GL-02.standard.normal[2]</t>
         </is>
       </c>
       <c r="E468" t="inlineStr" s="2">
@@ -15372,14 +15372,14 @@
       </c>
       <c r="F468" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒にいると練習も楽しいんだよな</t>
+          <t xml:space="preserve">もう少しスタミナつけないとな…</t>
         </is>
       </c>
     </row>
     <row r="469" ht="40" customHeight="1">
       <c r="A469" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.normal[1]</t>
         </is>
       </c>
       <c r="B469" t="inlineStr" s="2">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="D469" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.normal[2]</t>
+          <t xml:space="preserve">GL-03.down.standard.normal[1]</t>
         </is>
       </c>
       <c r="E469" t="inlineStr" s="2">
@@ -15404,14 +15404,14 @@
       </c>
       <c r="F469" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近調子良さそうだな。嬉しいな</t>
+          <t xml:space="preserve">最近…なんだか扱いが雑じゃないか…？</t>
         </is>
       </c>
     </row>
     <row r="470" ht="40" customHeight="1">
       <c r="A470" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.normal[2]</t>
         </is>
       </c>
       <c r="B470" t="inlineStr" s="2">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="D470" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.normal[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.normal[2]</t>
         </is>
       </c>
       <c r="E470" t="inlineStr" s="2">
@@ -15436,14 +15436,14 @@
       </c>
       <c r="F470" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今何してるかな…気になる</t>
+          <t xml:space="preserve">ちょっと不安になってきた…大丈夫かな</t>
         </is>
       </c>
     </row>
     <row r="471" ht="40" customHeight="1">
       <c r="A471" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.normal[1]</t>
         </is>
       </c>
       <c r="B471" t="inlineStr" s="2">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="D471" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.normal[2]</t>
+          <t xml:space="preserve">GL-03.up.standard.normal[1]</t>
         </is>
       </c>
       <c r="E471" t="inlineStr" s="2">
@@ -15468,14 +15468,14 @@
       </c>
       <c r="F471" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ったって聞くと…悔しいな</t>
+          <t xml:space="preserve">最近いい感じだ。この団体で頑張ろうって思える</t>
         </is>
       </c>
     </row>
     <row r="472" ht="40" customHeight="1">
       <c r="A472" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.normal[2]</t>
         </is>
       </c>
       <c r="B472" t="inlineStr" s="2">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="D472" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.normal[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.normal[2]</t>
         </is>
       </c>
       <c r="E472" t="inlineStr" s="2">
@@ -15500,14 +15500,14 @@
       </c>
       <c r="F472" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今週は出番なしか…リングが恋しい</t>
+          <t xml:space="preserve">ちゃんと見てくれてるんだな。嬉しいよ</t>
         </is>
       </c>
     </row>
     <row r="473" ht="40" customHeight="1">
       <c r="A473" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.normal[1]</t>
         </is>
       </c>
       <c r="B473" t="inlineStr" s="2">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="D473" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.normal[2]</t>
+          <t xml:space="preserve">GL-04.standard.normal[1]</t>
         </is>
       </c>
       <c r="E473" t="inlineStr" s="2">
@@ -15532,14 +15532,14 @@
       </c>
       <c r="F473" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合に出たい。見てるだけはつらい</t>
+          <t xml:space="preserve">一緒にいると練習も楽しいんだよな</t>
         </is>
       </c>
     </row>
     <row r="474" ht="40" customHeight="1">
       <c r="A474" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.normal[2]</t>
         </is>
       </c>
       <c r="B474" t="inlineStr" s="2">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="D474" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.normal[1]</t>
+          <t xml:space="preserve">GL-04.standard.normal[2]</t>
         </is>
       </c>
       <c r="E474" t="inlineStr" s="2">
@@ -15564,14 +15564,14 @@
       </c>
       <c r="F474" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が重い…コンディションが上がらない</t>
+          <t xml:space="preserve">最近調子良さそうだな。嬉しいな</t>
         </is>
       </c>
     </row>
     <row r="475" ht="40" customHeight="1">
       <c r="A475" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.normal[1]</t>
         </is>
       </c>
       <c r="B475" t="inlineStr" s="2">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="D475" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.normal[2]</t>
+          <t xml:space="preserve">GL-05.standard.normal[1]</t>
         </is>
       </c>
       <c r="E475" t="inlineStr" s="2">
@@ -15596,14 +15596,14 @@
       </c>
       <c r="F475" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子悪いな…少し休んだ方がいいかも</t>
+          <t xml:space="preserve">今何してるかな…気になる</t>
         </is>
       </c>
     </row>
     <row r="476" ht="40" customHeight="1">
       <c r="A476" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.normal[2]</t>
         </is>
       </c>
       <c r="B476" t="inlineStr" s="2">
@@ -15618,7 +15618,7 @@
       </c>
       <c r="D476" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.normal[1]</t>
+          <t xml:space="preserve">GL-05.standard.normal[2]</t>
         </is>
       </c>
       <c r="E476" t="inlineStr" s="2">
@@ -15628,14 +15628,14 @@
       </c>
       <c r="F476" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また負けた…どうすればいいんだ</t>
+          <t xml:space="preserve">勝ったって聞くと…悔しいな</t>
         </is>
       </c>
     </row>
     <row r="477" ht="40" customHeight="1">
       <c r="A477" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.normal[1]</t>
         </is>
       </c>
       <c r="B477" t="inlineStr" s="2">
@@ -15650,7 +15650,7 @@
       </c>
       <c r="D477" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.normal[2]</t>
+          <t xml:space="preserve">GL-06.standard.normal[1]</t>
         </is>
       </c>
       <c r="E477" t="inlineStr" s="2">
@@ -15660,14 +15660,14 @@
       </c>
       <c r="F477" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連敗が止まらない…自信がなくなってきた</t>
+          <t xml:space="preserve">今週は出番なしか…リングが恋しい</t>
         </is>
       </c>
     </row>
     <row r="478" ht="40" customHeight="1">
       <c r="A478" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.normal[2]</t>
         </is>
       </c>
       <c r="B478" t="inlineStr" s="2">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="D478" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.normal[1]</t>
+          <t xml:space="preserve">GL-06.standard.normal[2]</t>
         </is>
       </c>
       <c r="E478" t="inlineStr" s="2">
@@ -15692,14 +15692,14 @@
       </c>
       <c r="F478" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい流れが来てる。この調子を維持したい</t>
+          <t xml:space="preserve">試合に出たい。見てるだけはつらい</t>
         </is>
       </c>
     </row>
     <row r="479" ht="40" customHeight="1">
       <c r="A479" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.normal[1]</t>
         </is>
       </c>
       <c r="B479" t="inlineStr" s="2">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="D479" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.normal[2]</t>
+          <t xml:space="preserve">GL-07.standard.normal[1]</t>
         </is>
       </c>
       <c r="E479" t="inlineStr" s="2">
@@ -15724,14 +15724,14 @@
       </c>
       <c r="F479" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝中…自信がついてきた</t>
+          <t xml:space="preserve">体が重い…コンディションが上がらない</t>
         </is>
       </c>
     </row>
     <row r="480" ht="40" customHeight="1">
       <c r="A480" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.normal[2]</t>
         </is>
       </c>
       <c r="B480" t="inlineStr" s="2">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="D480" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.normal[1]</t>
+          <t xml:space="preserve">GL-07.standard.normal[2]</t>
         </is>
       </c>
       <c r="E480" t="inlineStr" s="2">
@@ -15756,14 +15756,14 @@
       </c>
       <c r="F480" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早くリングに戻りたい…体が疼く</t>
+          <t xml:space="preserve">調子悪いな…少し休んだ方がいいかも</t>
         </is>
       </c>
     </row>
     <row r="481" ht="40" customHeight="1">
       <c r="A481" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.normal[1]</t>
         </is>
       </c>
       <c r="B481" t="inlineStr" s="2">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="D481" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.normal[2]</t>
+          <t xml:space="preserve">GL-08.standard.normal[1]</t>
         </is>
       </c>
       <c r="E481" t="inlineStr" s="2">
@@ -15788,14 +15788,14 @@
       </c>
       <c r="F481" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">怪我…早く治さないと…</t>
+          <t xml:space="preserve">また負けた…どうすればいいんだ</t>
         </is>
       </c>
     </row>
     <row r="482" ht="40" customHeight="1">
       <c r="A482" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.normal[2]</t>
         </is>
       </c>
       <c r="B482" t="inlineStr" s="2">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="D482" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.standard.normal[1]</t>
+          <t xml:space="preserve">GL-08.standard.normal[2]</t>
         </is>
       </c>
       <c r="E482" t="inlineStr" s="2">
@@ -15820,14 +15820,14 @@
       </c>
       <c r="F482" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの子のこと？……特に何も。視界に入れてないだけ</t>
+          <t xml:space="preserve">連敗が止まらない…自信がなくなってきた</t>
         </is>
       </c>
     </row>
     <row r="483" ht="40" customHeight="1">
       <c r="A483" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.normal[1]</t>
         </is>
       </c>
       <c r="B483" t="inlineStr" s="2">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="D483" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-11.standard.normal[2]</t>
+          <t xml:space="preserve">GL-09.standard.normal[1]</t>
         </is>
       </c>
       <c r="E483" t="inlineStr" s="2">
@@ -15852,14 +15852,14 @@
       </c>
       <c r="F483" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">同じ場にいても、話すことは何もないかな</t>
+          <t xml:space="preserve">いい流れが来てる。この調子を維持したい</t>
         </is>
       </c>
     </row>
     <row r="484" ht="40" customHeight="1">
       <c r="A484" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.normal[2]</t>
         </is>
       </c>
       <c r="B484" t="inlineStr" s="2">
@@ -15869,12 +15869,12 @@
       </c>
       <c r="C484" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D484" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">GL-09.standard.normal[2]</t>
         </is>
       </c>
       <c r="E484" t="inlineStr" s="2">
@@ -15884,14 +15884,14 @@
       </c>
       <c r="F484" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調は終わったけど…あの期間は無駄じゃなかった</t>
+          <t xml:space="preserve">連勝中…自信がついてきた</t>
         </is>
       </c>
     </row>
     <row r="485" ht="40" customHeight="1">
       <c r="A485" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.normal[1]</t>
         </is>
       </c>
       <c r="B485" t="inlineStr" s="2">
@@ -15901,12 +15901,12 @@
       </c>
       <c r="C485" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D485" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">GL-10.standard.normal[1]</t>
         </is>
       </c>
       <c r="E485" t="inlineStr" s="2">
@@ -15916,14 +15916,14 @@
       </c>
       <c r="F485" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が落ち着いてきた。でも前より強くなってる気がする</t>
+          <t xml:space="preserve">早くリングに戻りたい…体が疼く</t>
         </is>
       </c>
     </row>
     <row r="486" ht="40" customHeight="1">
       <c r="A486" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.normal[2]</t>
         </is>
       </c>
       <c r="B486" t="inlineStr" s="2">
@@ -15933,29 +15933,29 @@
       </c>
       <c r="C486" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D486" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.normal[1]</t>
+          <t xml:space="preserve">GL-10.standard.normal[2]</t>
         </is>
       </c>
       <c r="E486" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F486" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちこち痛むけど、ここまで残った。最後まで、リングは渡さない</t>
+          <t xml:space="preserve">怪我…早く治さないと…</t>
         </is>
       </c>
     </row>
     <row r="487" ht="40" customHeight="1">
       <c r="A487" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.normal[1]</t>
         </is>
       </c>
       <c r="B487" t="inlineStr" s="2">
@@ -15965,29 +15965,29 @@
       </c>
       <c r="C487" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D487" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.normal[2]</t>
+          <t xml:space="preserve">GL-11.standard.normal[1]</t>
         </is>
       </c>
       <c r="E487" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F487" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重い。でも、あと一つ。繋いできたものを、無駄にはしない</t>
+          <t xml:space="preserve">あの子のこと？……特に何も。視界に入れてないだけ</t>
         </is>
       </c>
     </row>
     <row r="488" ht="40" customHeight="1">
       <c r="A488" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-11.standard.normal[2]</t>
         </is>
       </c>
       <c r="B488" t="inlineStr" s="2">
@@ -15997,29 +15997,29 @@
       </c>
       <c r="C488" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D488" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.normal[1]</t>
+          <t xml:space="preserve">GL-11.standard.normal[2]</t>
         </is>
       </c>
       <c r="E488" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F488" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どんな相手が来ても、やることは一つ。真っ向から受けて、次に繋ぐ</t>
+          <t xml:space="preserve">同じ場にいても、話すことは何もないかな</t>
         </is>
       </c>
     </row>
     <row r="489" ht="40" customHeight="1">
       <c r="A489" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.normal[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B489" t="inlineStr" s="2">
@@ -16029,29 +16029,29 @@
       </c>
       <c r="C489" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D489" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E489" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F489" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このリングは譲らない。目の前の一人に、全部ぶつけるだけ</t>
+          <t xml:space="preserve">絶好調は終わったけど…あの期間は無駄じゃなかった</t>
         </is>
       </c>
     </row>
     <row r="490" ht="40" customHeight="1">
       <c r="A490" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.normal[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B490" t="inlineStr" s="2">
@@ -16061,29 +16061,29 @@
       </c>
       <c r="C490" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D490" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E490" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F490" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、落とした。…息が上がってる。でも、リングは渡さない。次、来い</t>
+          <t xml:space="preserve">体が落ち着いてきた。でも前より強くなってる気がする</t>
         </is>
       </c>
     </row>
     <row r="491" ht="40" customHeight="1">
       <c r="A491" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.normal[1]</t>
         </is>
       </c>
       <c r="B491" t="inlineStr" s="2">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="D491" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.normal[2]</t>
+          <t xml:space="preserve">preFinal.standard.normal[1]</t>
         </is>
       </c>
       <c r="E491" t="inlineStr" s="2">
@@ -16108,14 +16108,14 @@
       </c>
       <c r="F491" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってる。次の挑戦者、早く出てきて。ここは動かないから</t>
+          <t xml:space="preserve">あちこち痛むけど、ここまで残った。最後まで、リングは渡さない</t>
         </is>
       </c>
     </row>
     <row r="492" ht="40" customHeight="1">
       <c r="A492" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.normal[2]</t>
         </is>
       </c>
       <c r="B492" t="inlineStr" s="2">
@@ -16125,12 +16125,12 @@
       </c>
       <c r="C492" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D492" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[1]</t>
+          <t xml:space="preserve">preFinal.standard.normal[2]</t>
         </is>
       </c>
       <c r="E492" t="inlineStr" s="2">
@@ -16140,14 +16140,14 @@
       </c>
       <c r="F492" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私一人の勝利じゃない。先鋒から大将まで、三人でつないだ勝利です</t>
+          <t xml:space="preserve">身体は重い。でも、あと一つ。繋いできたものを、無駄にはしない</t>
         </is>
       </c>
     </row>
     <row r="493" ht="40" customHeight="1">
       <c r="A493" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.normal[1]</t>
         </is>
       </c>
       <c r="B493" t="inlineStr" s="2">
@@ -16157,12 +16157,12 @@
       </c>
       <c r="C493" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D493" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[2]</t>
+          <t xml:space="preserve">preMatch.standard.normal[1]</t>
         </is>
       </c>
       <c r="E493" t="inlineStr" s="2">
@@ -16172,14 +16172,14 @@
       </c>
       <c r="F493" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人の力を合わせて、ここまで来ました。一人じゃ絶対にたどり着けなかった</t>
+          <t xml:space="preserve">どんな相手が来ても、やることは一つ。真っ向から受けて、次に繋ぐ</t>
         </is>
       </c>
     </row>
     <row r="494" ht="40" customHeight="1">
       <c r="A494" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.normal[2]</t>
         </is>
       </c>
       <c r="B494" t="inlineStr" s="2">
@@ -16189,12 +16189,12 @@
       </c>
       <c r="C494" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D494" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[3]</t>
+          <t xml:space="preserve">preMatch.standard.normal[2]</t>
         </is>
       </c>
       <c r="E494" t="inlineStr" s="2">
@@ -16204,14 +16204,14 @@
       </c>
       <c r="F494" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が繋いでくれたから、私はこのリングに立てている。感謝しかない</t>
+          <t xml:space="preserve">このリングは譲らない。目の前の一人に、全部ぶつけるだけ</t>
         </is>
       </c>
     </row>
     <row r="495" ht="40" customHeight="1">
       <c r="A495" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.normal[1]</t>
         </is>
       </c>
       <c r="B495" t="inlineStr" s="2">
@@ -16221,12 +16221,12 @@
       </c>
       <c r="C495" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D495" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.normal[1]</t>
+          <t xml:space="preserve">survivor.standard.normal[1]</t>
         </is>
       </c>
       <c r="E495" t="inlineStr" s="2">
@@ -16236,14 +16236,14 @@
       </c>
       <c r="F495" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPでも、団体が負けた事実は消えない。次は、最後の一人まで残ります</t>
+          <t xml:space="preserve">一人、落とした。…息が上がってる。でも、リングは渡さない。次、来い</t>
         </is>
       </c>
     </row>
     <row r="496" ht="40" customHeight="1">
       <c r="A496" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.normal[2]</t>
         </is>
       </c>
       <c r="B496" t="inlineStr" s="2">
@@ -16253,12 +16253,12 @@
       </c>
       <c r="C496" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D496" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.normal[2]</t>
+          <t xml:space="preserve">survivor.standard.normal[2]</t>
         </is>
       </c>
       <c r="E496" t="inlineStr" s="2">
@@ -16268,14 +16268,14 @@
       </c>
       <c r="F496" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この賞は嬉しい。でも、それだけじゃ足りない。次は団体ごと勝つ</t>
+          <t xml:space="preserve">まだ立ってる。次の挑戦者、早く出てきて。ここは動かないから</t>
         </is>
       </c>
     </row>
     <row r="497" ht="40" customHeight="1">
       <c r="A497" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[1]</t>
         </is>
       </c>
       <c r="B497" t="inlineStr" s="2">
@@ -16290,7 +16290,7 @@
       </c>
       <c r="D497" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.normal[3]</t>
+          <t xml:space="preserve">champion.standard.normal[1]</t>
         </is>
       </c>
       <c r="E497" t="inlineStr" s="2">
@@ -16300,14 +16300,14 @@
       </c>
       <c r="F497" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人の評価で満足するわけにはいかない。次こそ、みんなで頂点に立つ</t>
+          <t xml:space="preserve">私一人の勝利じゃない。先鋒から大将まで、三人でつないだ勝利です</t>
         </is>
       </c>
     </row>
     <row r="498" ht="40" customHeight="1">
       <c r="A498" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[2]</t>
         </is>
       </c>
       <c r="B498" t="inlineStr" s="2">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="D498" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.normal[1]</t>
+          <t xml:space="preserve">champion.standard.normal[2]</t>
         </is>
       </c>
       <c r="E498" t="inlineStr" s="2">
@@ -16332,14 +16332,14 @@
       </c>
       <c r="F498" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">脚がもう動かない。でも、最後までリングを譲らなかった。それだけは誇っていいと思う</t>
+          <t xml:space="preserve">三人の力を合わせて、ここまで来ました。一人じゃ絶対にたどり着けなかった</t>
         </is>
       </c>
     </row>
     <row r="499" ht="40" customHeight="1">
       <c r="A499" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.normal[3]</t>
         </is>
       </c>
       <c r="B499" t="inlineStr" s="2">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="D499" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.normal[2]</t>
+          <t xml:space="preserve">champion.standard.normal[3]</t>
         </is>
       </c>
       <c r="E499" t="inlineStr" s="2">
@@ -16364,14 +16364,14 @@
       </c>
       <c r="F499" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人倒したか、もう数えてない。ただ、一度も膝をつかなかった。それだけ覚えてる</t>
+          <t xml:space="preserve">仲間が繋いでくれたから、私はこのリングに立てている。感謝しかない</t>
         </is>
       </c>
     </row>
     <row r="500" ht="40" customHeight="1">
       <c r="A500" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[1]</t>
         </is>
       </c>
       <c r="B500" t="inlineStr" s="2">
@@ -16386,7 +16386,7 @@
       </c>
       <c r="D500" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.normal[3]</t>
+          <t xml:space="preserve">defiant.standard.normal[1]</t>
         </is>
       </c>
       <c r="E500" t="inlineStr" s="2">
@@ -16396,14 +16396,14 @@
       </c>
       <c r="F500" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぼろぼろだけど、立ってる。それが今日の私の答え</t>
+          <t xml:space="preserve">MVPでも、団体が負けた事実は消えない。次は、最後の一人まで残ります</t>
         </is>
       </c>
     </row>
     <row r="501" ht="40" customHeight="1">
       <c r="A501" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[2]</t>
         </is>
       </c>
       <c r="B501" t="inlineStr" s="2">
@@ -16413,12 +16413,12 @@
       </c>
       <c r="C501" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D501" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[1]</t>
+          <t xml:space="preserve">defiant.standard.normal[2]</t>
         </is>
       </c>
       <c r="E501" t="inlineStr" s="2">
@@ -16428,14 +16428,14 @@
       </c>
       <c r="F501" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この優勝を、次のステップにする</t>
+          <t xml:space="preserve">この賞は嬉しい。でも、それだけじゃ足りない。次は団体ごと勝つ</t>
         </is>
       </c>
     </row>
     <row r="502" ht="40" customHeight="1">
       <c r="A502" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.normal[3]</t>
         </is>
       </c>
       <c r="B502" t="inlineStr" s="2">
@@ -16445,12 +16445,12 @@
       </c>
       <c r="C502" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D502" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.normal[2]</t>
+          <t xml:space="preserve">defiant.standard.normal[3]</t>
         </is>
       </c>
       <c r="E502" t="inlineStr" s="2">
@@ -16460,14 +16460,14 @@
       </c>
       <c r="F502" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">優勝。嬉しい。でも、これで終わりじゃない</t>
+          <t xml:space="preserve">個人の評価で満足するわけにはいかない。次こそ、みんなで頂点に立つ</t>
         </is>
       </c>
     </row>
     <row r="503" ht="40" customHeight="1">
       <c r="A503" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[1]</t>
         </is>
       </c>
       <c r="B503" t="inlineStr" s="2">
@@ -16477,12 +16477,12 @@
       </c>
       <c r="C503" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D503" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.normal[1]</t>
+          <t xml:space="preserve">gauntlet.standard.normal[1]</t>
         </is>
       </c>
       <c r="E503" t="inlineStr" s="2">
@@ -16492,14 +16492,14 @@
       </c>
       <c r="F503" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しい…。でも、次に繋げる</t>
+          <t xml:space="preserve">脚がもう動かない。でも、最後までリングを譲らなかった。それだけは誇っていいと思う</t>
         </is>
       </c>
     </row>
     <row r="504" ht="40" customHeight="1">
       <c r="A504" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.normal[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[2]</t>
         </is>
       </c>
       <c r="B504" t="inlineStr" s="2">
@@ -16509,12 +16509,12 @@
       </c>
       <c r="C504" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D504" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.normal[2]</t>
+          <t xml:space="preserve">gauntlet.standard.normal[2]</t>
         </is>
       </c>
       <c r="E504" t="inlineStr" s="2">
@@ -16524,14 +16524,14 @@
       </c>
       <c r="F504" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">力不足を痛感した。もっと強くならないと</t>
+          <t xml:space="preserve">何人倒したか、もう数えてない。ただ、一度も膝をつかなかった。それだけ覚えてる</t>
         </is>
       </c>
     </row>
     <row r="505" ht="40" customHeight="1">
       <c r="A505" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.normal[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.normal[3]</t>
         </is>
       </c>
       <c r="B505" t="inlineStr" s="2">
@@ -16541,12 +16541,12 @@
       </c>
       <c r="C505" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D505" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.normal[1]</t>
+          <t xml:space="preserve">gauntlet.standard.normal[3]</t>
         </is>
       </c>
       <c r="E505" t="inlineStr" s="2">
@@ -16556,14 +16556,14 @@
       </c>
       <c r="F505" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一つクリア。次に集中する</t>
+          <t xml:space="preserve">ぼろぼろだけど、立ってる。それが今日の私の答え</t>
         </is>
       </c>
     </row>
     <row r="506" ht="40" customHeight="1">
       <c r="A506" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.normal[1]</t>
         </is>
       </c>
       <c r="B506" t="inlineStr" s="2">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="D506" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.normal[2]</t>
+          <t xml:space="preserve">champion.standard.normal[1]</t>
         </is>
       </c>
       <c r="E506" t="inlineStr" s="2">
@@ -16588,14 +16588,14 @@
       </c>
       <c r="F506" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った。でも気を抜かない</t>
+          <t xml:space="preserve">この優勝を、次のステップにする</t>
         </is>
       </c>
     </row>
     <row r="507" ht="40" customHeight="1">
       <c r="A507" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.normal[2]</t>
         </is>
       </c>
       <c r="B507" t="inlineStr" s="2">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="D507" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.normal[1]</t>
+          <t xml:space="preserve">champion.standard.normal[2]</t>
         </is>
       </c>
       <c r="E507" t="inlineStr" s="2">
@@ -16620,14 +16620,14 @@
       </c>
       <c r="F507" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい経験になった。もっと強くなりたい</t>
+          <t xml:space="preserve">優勝。嬉しい。でも、これで終わりじゃない</t>
         </is>
       </c>
     </row>
     <row r="508" ht="40" customHeight="1">
       <c r="A508" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.normal[1]</t>
         </is>
       </c>
       <c r="B508" t="inlineStr" s="2">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="D508" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.normal[2]</t>
+          <t xml:space="preserve">postLose.standard.normal[1]</t>
         </is>
       </c>
       <c r="E508" t="inlineStr" s="2">
@@ -16652,14 +16652,14 @@
       </c>
       <c r="F508" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大会を通して、自分の成長を感じられた</t>
+          <t xml:space="preserve">悔しい…。でも、次に繋げる</t>
         </is>
       </c>
     </row>
     <row r="509" ht="40" customHeight="1">
       <c r="A509" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.normal[2]</t>
         </is>
       </c>
       <c r="B509" t="inlineStr" s="2">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="D509" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.normal[1]</t>
+          <t xml:space="preserve">postLose.standard.normal[2]</t>
         </is>
       </c>
       <c r="E509" t="inlineStr" s="2">
@@ -16684,14 +16684,14 @@
       </c>
       <c r="F509" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あと一つ。勝てば優勝。それだけ考える</t>
+          <t xml:space="preserve">力不足を痛感した。もっと強くならないと</t>
         </is>
       </c>
     </row>
     <row r="510" ht="40" customHeight="1">
       <c r="A510" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="B510" t="inlineStr" s="2">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="D510" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.normal[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="E510" t="inlineStr" s="2">
@@ -16716,14 +16716,14 @@
       </c>
       <c r="F510" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決勝。全てを懸ける</t>
+          <t xml:space="preserve">一つクリア。次に集中する</t>
         </is>
       </c>
     </row>
     <row r="511" ht="40" customHeight="1">
       <c r="A511" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="B511" t="inlineStr" s="2">
@@ -16738,7 +16738,7 @@
       </c>
       <c r="D511" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.normal[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="E511" t="inlineStr" s="2">
@@ -16748,14 +16748,14 @@
       </c>
       <c r="F511" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手がどうとかじゃない。自分の試合をする</t>
+          <t xml:space="preserve">勝った。でも気を抜かない</t>
         </is>
       </c>
     </row>
     <row r="512" ht="40" customHeight="1">
       <c r="A512" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="B512" t="inlineStr" s="2">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="D512" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.normal[2]</t>
+          <t xml:space="preserve">postWin.standard.normal[1]</t>
         </is>
       </c>
       <c r="E512" t="inlineStr" s="2">
@@ -16780,14 +16780,14 @@
       </c>
       <c r="F512" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">集中。一つずつ勝っていく</t>
+          <t xml:space="preserve">いい経験になった。もっと強くなりたい</t>
         </is>
       </c>
     </row>
     <row r="513" ht="40" customHeight="1">
       <c r="A513" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="B513" t="inlineStr" s="2">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="D513" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.normal[1]</t>
+          <t xml:space="preserve">postWin.standard.normal[2]</t>
         </is>
       </c>
       <c r="E513" t="inlineStr" s="2">
@@ -16812,14 +16812,14 @@
       </c>
       <c r="F513" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選ばれたからには、全力で戦う</t>
+          <t xml:space="preserve">大会を通して、自分の成長を感じられた</t>
         </is>
       </c>
     </row>
     <row r="514" ht="40" customHeight="1">
       <c r="A514" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.normal[1]</t>
         </is>
       </c>
       <c r="B514" t="inlineStr" s="2">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="D514" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.normal[2]</t>
+          <t xml:space="preserve">preFinal.standard.normal[1]</t>
         </is>
       </c>
       <c r="E514" t="inlineStr" s="2">
@@ -16844,14 +16844,14 @@
       </c>
       <c r="F514" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この舞台に立てることを誇りに思う</t>
+          <t xml:space="preserve">あと一つ。勝てば優勝。それだけ考える</t>
         </is>
       </c>
     </row>
     <row r="515" ht="40" customHeight="1">
       <c r="A515" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.normal[2]</t>
         </is>
       </c>
       <c r="B515" t="inlineStr" s="2">
@@ -16861,12 +16861,12 @@
       </c>
       <c r="C515" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D515" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">preFinal.standard.normal[2]</t>
         </is>
       </c>
       <c r="E515" t="inlineStr" s="2">
@@ -16876,14 +16876,14 @@
       </c>
       <c r="F515" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悪いけど、今日は負けるわけにはいかないの</t>
+          <t xml:space="preserve">決勝。全てを懸ける</t>
         </is>
       </c>
     </row>
     <row r="516" ht="40" customHeight="1">
       <c r="A516" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.normal[1]</t>
         </is>
       </c>
       <c r="B516" t="inlineStr" s="2">
@@ -16893,12 +16893,12 @@
       </c>
       <c r="C516" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D516" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">preMatch.standard.normal[1]</t>
         </is>
       </c>
       <c r="E516" t="inlineStr" s="2">
@@ -16908,14 +16908,14 @@
       </c>
       <c r="F516" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この大舞台、最高の気分ね</t>
+          <t xml:space="preserve">相手がどうとかじゃない。自分の試合をする</t>
         </is>
       </c>
     </row>
     <row r="517" ht="40" customHeight="1">
       <c r="A517" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.normal[2]</t>
         </is>
       </c>
       <c r="B517" t="inlineStr" s="2">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="C517" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D517" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">preMatch.standard.normal[2]</t>
         </is>
       </c>
       <c r="E517" t="inlineStr" s="2">
@@ -16940,14 +16940,14 @@
       </c>
       <c r="F517" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正々堂々、最高の試合にしましょう</t>
+          <t xml:space="preserve">集中。一つずつ勝っていく</t>
         </is>
       </c>
     </row>
     <row r="518" ht="40" customHeight="1">
       <c r="A518" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.normal[1]</t>
         </is>
       </c>
       <c r="B518" t="inlineStr" s="2">
@@ -16957,12 +16957,12 @@
       </c>
       <c r="C518" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D518" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">summon.standard.normal[1]</t>
         </is>
       </c>
       <c r="E518" t="inlineStr" s="2">
@@ -16972,14 +16972,14 @@
       </c>
       <c r="F518" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……やった。本当に、やったんだ……！</t>
+          <t xml:space="preserve">選ばれたからには、全力で戦う</t>
         </is>
       </c>
     </row>
     <row r="519" ht="40" customHeight="1">
       <c r="A519" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.normal[2]</t>
         </is>
       </c>
       <c r="B519" t="inlineStr" s="2">
@@ -16989,12 +16989,12 @@
       </c>
       <c r="C519" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D519" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">summon.standard.normal[2]</t>
         </is>
       </c>
       <c r="E519" t="inlineStr" s="2">
@@ -17004,14 +17004,14 @@
       </c>
       <c r="F519" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなのおかげです。この舞台で勝てて、本当に嬉しい</t>
+          <t xml:space="preserve">この舞台に立てることを誇りに思う</t>
         </is>
       </c>
     </row>
     <row r="520" ht="40" customHeight="1">
       <c r="A520" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B520" t="inlineStr" s="2">
@@ -17021,12 +17021,12 @@
       </c>
       <c r="C520" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D520" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E520" t="inlineStr" s="2">
@@ -17036,14 +17036,14 @@
       </c>
       <c r="F520" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じてくれた人たちに、やっと恩返しができた気がする</t>
+          <t xml:space="preserve">悪いけど、今日は負けるわけにはいかないの</t>
         </is>
       </c>
     </row>
     <row r="521" ht="40" customHeight="1">
       <c r="A521" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.normal[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B521" t="inlineStr" s="2">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="C521" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D521" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E521" t="inlineStr" s="2">
@@ -17068,14 +17068,14 @@
       </c>
       <c r="F521" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたたちの実力、確かめさせてもらうよ</t>
+          <t xml:space="preserve">この大舞台、最高の気分ね</t>
         </is>
       </c>
     </row>
     <row r="522" ht="40" customHeight="1">
       <c r="A522" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.normal[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B522" t="inlineStr" s="2">
@@ -17085,12 +17085,12 @@
       </c>
       <c r="C522" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D522" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E522" t="inlineStr" s="2">
@@ -17100,14 +17100,14 @@
       </c>
       <c r="F522" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こっちは本気だよ。受けて立つ気はある？</t>
+          <t xml:space="preserve">正々堂々、最高の試合にしましょう</t>
         </is>
       </c>
     </row>
     <row r="523" ht="40" customHeight="1">
       <c r="A523" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B523" t="inlineStr" s="2">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="C523" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D523" t="inlineStr" s="12">
@@ -17132,14 +17132,14 @@
       </c>
       <c r="F523" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっぱりね。逃げるだろうなって思ってた</t>
+          <t xml:space="preserve">……やった。本当に、やったんだ……！</t>
         </is>
       </c>
     </row>
     <row r="524" ht="40" customHeight="1">
       <c r="A524" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.normal[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B524" t="inlineStr" s="2">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="C524" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D524" t="inlineStr" s="12">
@@ -17164,14 +17164,14 @@
       </c>
       <c r="F524" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…逃げ足だけは速いんだね</t>
+          <t xml:space="preserve">みんなのおかげです。この舞台で勝てて、本当に嬉しい</t>
         </is>
       </c>
     </row>
     <row r="525" ht="40" customHeight="1">
       <c r="A525" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.normal[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B525" t="inlineStr" s="2">
@@ -17181,12 +17181,12 @@
       </c>
       <c r="C525" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D525" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E525" t="inlineStr" s="2">
@@ -17196,14 +17196,14 @@
       </c>
       <c r="F525" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど…結果は結果。次は絶対に負けない</t>
+          <t xml:space="preserve">信じてくれた人たちに、やっと恩返しができた気がする</t>
         </is>
       </c>
     </row>
     <row r="526" ht="40" customHeight="1">
       <c r="A526" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.normal[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.normal[1]</t>
         </is>
       </c>
       <c r="B526" t="inlineStr" s="2">
@@ -17213,12 +17213,12 @@
       </c>
       <c r="C526" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D526" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E526" t="inlineStr" s="2">
@@ -17228,14 +17228,14 @@
       </c>
       <c r="F526" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借りは…必ず返す</t>
+          <t xml:space="preserve">あんたたちの実力、確かめさせてもらうよ</t>
         </is>
       </c>
     </row>
     <row r="527" ht="40" customHeight="1">
       <c r="A527" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.normal[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.normal[2]</t>
         </is>
       </c>
       <c r="B527" t="inlineStr" s="2">
@@ -17245,12 +17245,12 @@
       </c>
       <c r="C527" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D527" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E527" t="inlineStr" s="2">
@@ -17260,14 +17260,14 @@
       </c>
       <c r="F527" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てた。うちの団体の強さを見せられたと思う</t>
+          <t xml:space="preserve">こっちは本気だよ。受けて立つ気はある？</t>
         </is>
       </c>
     </row>
     <row r="528" ht="40" customHeight="1">
       <c r="A528" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.normal[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.normal[1]</t>
         </is>
       </c>
       <c r="B528" t="inlineStr" s="2">
@@ -17277,12 +17277,12 @@
       </c>
       <c r="C528" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D528" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E528" t="inlineStr" s="2">
@@ -17292,14 +17292,14 @@
       </c>
       <c r="F528" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい対抗戦だった。この経験を次に活かそう</t>
+          <t xml:space="preserve">やっぱりね。逃げるだろうなって思ってた</t>
         </is>
       </c>
     </row>
     <row r="529" ht="40" customHeight="1">
       <c r="A529" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.normal[2]</t>
         </is>
       </c>
       <c r="B529" t="inlineStr" s="2">
@@ -17309,12 +17309,12 @@
       </c>
       <c r="C529" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D529" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E529" t="inlineStr" s="2">
@@ -17324,14 +17324,14 @@
       </c>
       <c r="F529" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うちの団体の強さ、見せられたと思います</t>
+          <t xml:space="preserve">…逃げ足だけは速いんだね</t>
         </is>
       </c>
     </row>
     <row r="530" ht="40" customHeight="1">
       <c r="A530" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.normal[1]</t>
         </is>
       </c>
       <c r="B530" t="inlineStr" s="2">
@@ -17341,12 +17341,12 @@
       </c>
       <c r="C530" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D530" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">result_lose.standard.normal[1]</t>
         </is>
       </c>
       <c r="E530" t="inlineStr" s="2">
@@ -17356,14 +17356,14 @@
       </c>
       <c r="F530" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝てて良かった。団体の看板は守れた</t>
+          <t xml:space="preserve">悔しいけど…結果は結果。次は絶対に負けない</t>
         </is>
       </c>
     </row>
     <row r="531" ht="40" customHeight="1">
       <c r="A531" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.normal[2]</t>
         </is>
       </c>
       <c r="B531" t="inlineStr" s="2">
@@ -17373,12 +17373,12 @@
       </c>
       <c r="C531" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D531" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">result_lose.standard.normal[2]</t>
         </is>
       </c>
       <c r="E531" t="inlineStr" s="2">
@@ -17388,14 +17388,14 @@
       </c>
       <c r="F531" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一つ勝てた。みんなの期待に応えられたかな</t>
+          <t xml:space="preserve">この借りは…必ず返す</t>
         </is>
       </c>
     </row>
     <row r="532" ht="40" customHeight="1">
       <c r="A532" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.normal[1]</t>
         </is>
       </c>
       <c r="B532" t="inlineStr" s="2">
@@ -17405,29 +17405,29 @@
       </c>
       <c r="C532" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D532" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.normal[1]</t>
+          <t xml:space="preserve">result_win.standard.normal[1]</t>
         </is>
       </c>
       <c r="E532" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F532" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体で戦えて、本当に良かった</t>
+          <t xml:space="preserve">勝てた。うちの団体の強さを見せられたと思う</t>
         </is>
       </c>
     </row>
     <row r="533" ht="40" customHeight="1">
       <c r="A533" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.normal[2]</t>
         </is>
       </c>
       <c r="B533" t="inlineStr" s="2">
@@ -17437,29 +17437,29 @@
       </c>
       <c r="C533" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D533" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.normal[2]</t>
+          <t xml:space="preserve">result_win.standard.normal[2]</t>
         </is>
       </c>
       <c r="E533" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F533" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">入団した時は、まさかここまで来れるなんて思わなかった</t>
+          <t xml:space="preserve">いい対抗戦だった。この経験を次に活かそう</t>
         </is>
       </c>
     </row>
     <row r="534" ht="40" customHeight="1">
       <c r="A534" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[1]</t>
         </is>
       </c>
       <c r="B534" t="inlineStr" s="2">
@@ -17469,29 +17469,29 @@
       </c>
       <c r="C534" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D534" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.normal[3]</t>
+          <t xml:space="preserve">standard.normal[1]</t>
         </is>
       </c>
       <c r="E534" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F534" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の仲間と、最高の舞台。感謝しかないよ</t>
+          <t xml:space="preserve">うちの団体の強さ、見せられたと思います</t>
         </is>
       </c>
     </row>
     <row r="535" ht="40" customHeight="1">
       <c r="A535" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[2]</t>
         </is>
       </c>
       <c r="B535" t="inlineStr" s="2">
@@ -17501,29 +17501,29 @@
       </c>
       <c r="C535" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D535" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">standard.normal[2]</t>
         </is>
       </c>
       <c r="E535" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F535" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">所属が決まるって、やっぱり落ち着くね</t>
+          <t xml:space="preserve">勝てて良かった。団体の看板は守れた</t>
         </is>
       </c>
     </row>
     <row r="536" ht="40" customHeight="1">
       <c r="A536" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.normal[3]</t>
         </is>
       </c>
       <c r="B536" t="inlineStr" s="2">
@@ -17533,29 +17533,29 @@
       </c>
       <c r="C536" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D536" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
       <c r="E536" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F536" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">また声がかかって嬉しいよ。今度は長くいたいね</t>
+          <t xml:space="preserve">一つ勝てた。みんなの期待に応えられたかな</t>
         </is>
       </c>
     </row>
     <row r="537" ht="40" customHeight="1">
       <c r="A537" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[3]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[1]</t>
         </is>
       </c>
       <c r="B537" t="inlineStr" s="2">
@@ -17565,29 +17565,29 @@
       </c>
       <c r="C537" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D537" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[3]</t>
+          <t xml:space="preserve">fighter.standard.normal[1]</t>
         </is>
       </c>
       <c r="E537" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F537" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーも気楽だったけど、やっぱりリングが一番だね</t>
+          <t xml:space="preserve">この団体で戦えて、本当に良かった</t>
         </is>
       </c>
     </row>
     <row r="538" ht="40" customHeight="1">
       <c r="A538" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.normal[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[2]</t>
         </is>
       </c>
       <c r="B538" t="inlineStr" s="2">
@@ -17597,29 +17597,29 @@
       </c>
       <c r="C538" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D538" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[1]</t>
+          <t xml:space="preserve">fighter.standard.normal[2]</t>
         </is>
       </c>
       <c r="E538" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F538" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくれた目を信じて、頑張ってみるね</t>
+          <t xml:space="preserve">入団した時は、まさかここまで来れるなんて思わなかった</t>
         </is>
       </c>
     </row>
     <row r="539" ht="40" customHeight="1">
       <c r="A539" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.normal[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.normal[3]</t>
         </is>
       </c>
       <c r="B539" t="inlineStr" s="2">
@@ -17629,59 +17629,219 @@
       </c>
       <c r="C539" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D539" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.normal[2]</t>
+          <t xml:space="preserve">fighter.standard.normal[3]</t>
         </is>
       </c>
       <c r="E539" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F539" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まさか自分に声がかかるとはね。よろしく</t>
+          <t xml:space="preserve">最高の仲間と、最高の舞台。感謝しかないよ</t>
         </is>
       </c>
     </row>
     <row r="540" ht="40" customHeight="1">
       <c r="A540" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">所属が決まるって、やっぱり落ち着くね</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="40" customHeight="1">
+      <c r="A541" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">また声がかかって嬉しいよ。今度は長くいたいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="40" customHeight="1">
+      <c r="A542" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.normal[3]</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[3]</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリーも気楽だったけど、やっぱりリングが一番だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="40" customHeight="1">
+      <c r="A543" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[1]</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてくれた目を信じて、頑張ってみるね</t>
+        </is>
+      </c>
+    </row>
+    <row r="544" ht="40" customHeight="1">
+      <c r="A544" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.normal[2]</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まさか自分に声がかかるとはね。よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="40" customHeight="1">
+      <c r="A545" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.normal[3]</t>
         </is>
       </c>
-      <c r="B540" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C540" t="inlineStr" s="2">
+      <c r="B545" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr" s="12">
+      <c r="D545" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.normal[3]</t>
         </is>
       </c>
-      <c r="E540" t="inlineStr" s="2">
+      <c r="E545" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F540" t="inlineStr" s="3">
+      <c r="F545" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">期待されてるうちに、いいとこ見せないとね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H540"/>
+  <autoFilter ref="A1:H545"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
@@ -3975,7 +3975,7 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お願いがあります。あの人とやらせてください。</t>
+          <t xml:space="preserve">社長、お願いがあります。三人であちらへ行かせてください。</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">どうしても、あの人とやりたいんです。……お願いします。</t>
+          <t xml:space="preserve">どうしても、三人で挑みたいんです。……お願いします。</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わがままだとは分かってます。それでも、組んでほしいんです。</t>
+          <t xml:space="preserve">わがままだとは分かってます。それでも、三人で組んでほしいんです。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×ノーマル.xlsx
@@ -15436,7 +15436,7 @@
       </c>
       <c r="F470" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次に当たったとき…絶対に見てろよ</t>
+          <t xml:space="preserve">次に当たったとき…絶対に見返してやる</t>
         </is>
       </c>
     </row>
